--- a/results/DR_results/01_pollution_assessment/HZD_Toxicity/tables/hzd_chemical_quotients.xlsx
+++ b/results/DR_results/01_pollution_assessment/HZD_Toxicity/tables/hzd_chemical_quotients.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1805668855497589</v>
+        <v>0.01822975585741975</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0664400292189779</v>
+        <v>0.005877387200140353</v>
       </c>
       <c r="D2" t="n">
-        <v>2.39551761830836</v>
+        <v>0.7106702267648134</v>
       </c>
       <c r="E2" t="n">
-        <v>1.283572446293739</v>
+        <v>0.255168016431888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2794659887537514</v>
+        <v>0.1092686838911064</v>
       </c>
       <c r="G2" t="n">
-        <v>0.35202460840465</v>
+        <v>0.07465756795695933</v>
       </c>
       <c r="H2" t="n">
-        <v>5463.483254901896</v>
+        <v>927.7613074361709</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1897419379464363</v>
+        <v>0.08862432081037251</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6321364703146014</v>
+        <v>0.1768006690411151</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001518232892561988</v>
+        <v>4.002313289760362e-05</v>
       </c>
     </row>
     <row r="3">
@@ -529,34 +529,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05776334249069262</v>
+        <v>0.00583169847509868</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01361770711593231</v>
+        <v>0.001204643321794012</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08508052935756243</v>
+        <v>0.02524055704274352</v>
       </c>
       <c r="E3" t="n">
-        <v>0.226982474149489</v>
+        <v>0.04512302196947672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2207089884560403</v>
+        <v>0.0862952261170464</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2758868408669208</v>
+        <v>0.05851022933821946</v>
       </c>
       <c r="H3" t="n">
-        <v>3605.323117772814</v>
+        <v>612.2246803765155</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1495257228270975</v>
+        <v>0.06984020387191593</v>
       </c>
       <c r="J3" t="n">
-        <v>1.117318435754067e-05</v>
+        <v>3.124999999999655e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004731031239669423</v>
+        <v>0.0001247178169934641</v>
       </c>
     </row>
     <row r="4">
@@ -566,34 +566,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1240337288474058</v>
+        <v>0.01252225505296493</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03688471725245524</v>
+        <v>0.00326287883387104</v>
       </c>
       <c r="D4" t="n">
-        <v>1.325727791979988</v>
+        <v>0.393299244954063</v>
       </c>
       <c r="E4" t="n">
-        <v>0.680544094607375</v>
+        <v>0.1352888862773697</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2084054357139658</v>
+        <v>0.08148464783771275</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1420115514307643</v>
+        <v>0.03011788607524934</v>
       </c>
       <c r="H4" t="n">
-        <v>3227.513094913829</v>
+        <v>548.0682614004616</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09926289612109057</v>
+        <v>0.04636353378495382</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3839178224922473</v>
+        <v>0.1073770159783004</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001940606859504135</v>
+        <v>5.115761002178658e-05</v>
       </c>
     </row>
     <row r="5">
@@ -603,34 +603,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3631417869544376</v>
+        <v>0.03666223791616686</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1005532322448838</v>
+        <v>0.008895093621662796</v>
       </c>
       <c r="D5" t="n">
-        <v>4.671066106158648</v>
+        <v>1.385749611493732</v>
       </c>
       <c r="E5" t="n">
-        <v>3.097486497251611</v>
+        <v>0.6157653880078502</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7580625817169309</v>
+        <v>0.2963956400586918</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9865142044558278</v>
+        <v>0.209220462153048</v>
       </c>
       <c r="H5" t="n">
-        <v>25549.32550204717</v>
+        <v>4338.564707894803</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7746756730817735</v>
+        <v>0.3618341106781123</v>
       </c>
       <c r="J5" t="n">
-        <v>1.315037706574429</v>
+        <v>0.3677996085575356</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002556304336088156</v>
+        <v>0.0006738841496005813</v>
       </c>
     </row>
     <row r="6">
@@ -640,34 +640,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05332989035247823</v>
+        <v>0.005384103946128792</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01221200876715947</v>
+        <v>0.001080293083248722</v>
       </c>
       <c r="D6" t="n">
-        <v>2.36771304971707</v>
+        <v>0.7024215380827306</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11462799249033</v>
+        <v>0.221582673205909</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2158208142054864</v>
+        <v>0.08438399402268566</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3952409190191664</v>
+        <v>0.08382290631547422</v>
       </c>
       <c r="H6" t="n">
-        <v>3886.652656431817</v>
+        <v>659.9976209035161</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09239372040773233</v>
+        <v>0.04315509163077209</v>
       </c>
       <c r="J6" t="n">
-        <v>0.543322057038747</v>
+        <v>0.1519603878280245</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0002782855206611568</v>
+        <v>7.336067102396507e-05</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.851187763616458</v>
+        <v>0.1868930777325242</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8684014775046504</v>
+        <v>0.07682013070233445</v>
       </c>
       <c r="D7" t="n">
-        <v>2.067750977496841</v>
+        <v>0.6134327899907295</v>
       </c>
       <c r="E7" t="n">
-        <v>1.058256387723233</v>
+        <v>0.2103762698485946</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2235947026453496</v>
+        <v>0.08742351436764118</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2323694918119261</v>
+        <v>0.04928104658561654</v>
       </c>
       <c r="H7" t="n">
-        <v>3223.098487423562</v>
+        <v>547.3186110719256</v>
       </c>
       <c r="I7" t="n">
-        <v>0.29102298603105</v>
+        <v>0.1359304893601818</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5163726350141198</v>
+        <v>0.1444229713555116</v>
       </c>
       <c r="K7" t="n">
-        <v>9.461922314049512e-05</v>
+        <v>2.494319389978194e-05</v>
       </c>
     </row>
     <row r="8">
@@ -714,34 +714,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1567768819039897</v>
+        <v>0.01582795357241557</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05969474495436935</v>
+        <v>0.005280688976732673</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2692876339083133</v>
+        <v>0.07988866472613294</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2963586171566217</v>
+        <v>0.05891466485643684</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3612502162913304</v>
+        <v>0.1412455800634571</v>
       </c>
       <c r="G8" t="n">
-        <v>0.530131713225612</v>
+        <v>0.1124306183753647</v>
       </c>
       <c r="H8" t="n">
-        <v>9648.704925607884</v>
+        <v>1638.459326990018</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1984471564333241</v>
+        <v>0.09269033849869251</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02011613337161906</v>
+        <v>0.005626231052374704</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0002581904628099183</v>
+        <v>6.806328104575187e-05</v>
       </c>
     </row>
     <row r="9">
@@ -751,34 +751,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4744283292134731</v>
+        <v>0.04789755655957108</v>
       </c>
       <c r="C9" t="n">
-        <v>0.399200613161892</v>
+        <v>0.03531390039509045</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02443508420613676</v>
+        <v>0.007249074981153906</v>
       </c>
       <c r="E9" t="n">
-        <v>0.264143604137494</v>
+        <v>0.05251047552130905</v>
       </c>
       <c r="F9" t="n">
-        <v>0.284442305459821</v>
+        <v>0.1112143788914976</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4827011768250272</v>
+        <v>0.1023715247494689</v>
       </c>
       <c r="H9" t="n">
-        <v>6261.124438585583</v>
+        <v>1063.209810325854</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3866263315998952</v>
+        <v>0.1805847268995395</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01365485714009737</v>
+        <v>0.003819092856370984</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0007015731900826451</v>
+        <v>0.0001849463093681918</v>
       </c>
     </row>
     <row r="10">
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.305945281715696</v>
+        <v>0.03088776646075397</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07958285950338065</v>
+        <v>0.007040022186837518</v>
       </c>
       <c r="D10" t="n">
-        <v>1.875482387096592</v>
+        <v>0.5563931081719891</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9426969539320668</v>
+        <v>0.1874036113238446</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2073451878146632</v>
+        <v>0.08107010046086829</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4262931132195455</v>
+        <v>0.09040847233380966</v>
       </c>
       <c r="H10" t="n">
-        <v>5553.060257678054</v>
+        <v>942.9724965868392</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1877087483630118</v>
+        <v>0.08767466230124213</v>
       </c>
       <c r="J10" t="n">
-        <v>0.455282912142328</v>
+        <v>0.1273369394898073</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0007637504462809917</v>
+        <v>0.0002013372636165577</v>
       </c>
     </row>
     <row r="11">
@@ -825,34 +825,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.403501461070981</v>
+        <v>0.04073688872154313</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1348836018937412</v>
+        <v>0.01193201093675402</v>
       </c>
       <c r="D11" t="n">
-        <v>2.437043714654198</v>
+        <v>0.7229896353474119</v>
       </c>
       <c r="E11" t="n">
-        <v>1.294005829280108</v>
+        <v>0.2572421226882142</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2999193868176445</v>
+        <v>0.1172657782692412</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4507134355284079</v>
+        <v>0.09558754740065564</v>
       </c>
       <c r="H11" t="n">
-        <v>5957.032853162727</v>
+        <v>1011.571616574803</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3053104361993833</v>
+        <v>0.1426038457145268</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5850233188481707</v>
+        <v>0.1636237094903477</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0009280748264462801</v>
+        <v>0.0002446558910675379</v>
       </c>
     </row>
     <row r="12">
@@ -862,34 +862,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7978842911350575</v>
+        <v>0.08055317444047226</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3761537898908731</v>
+        <v>0.03327514295188493</v>
       </c>
       <c r="D12" t="n">
-        <v>2.063986994413351</v>
+        <v>0.6123161416759606</v>
       </c>
       <c r="E12" t="n">
-        <v>1.318498398531244</v>
+        <v>0.2621111274188617</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4180949811559859</v>
+        <v>0.1634713710105386</v>
       </c>
       <c r="G12" t="n">
-        <v>0.359992454002426</v>
+        <v>0.07634739292937356</v>
       </c>
       <c r="H12" t="n">
-        <v>4546.151837125276</v>
+        <v>771.9880478137261</v>
       </c>
       <c r="I12" t="n">
-        <v>0.819162285599452</v>
+        <v>0.3826128371009786</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5929602805114853</v>
+        <v>0.165843578455556</v>
       </c>
       <c r="K12" t="n">
-        <v>0.002710846983471074</v>
+        <v>0.0007146241503267972</v>
       </c>
     </row>
     <row r="13">
@@ -899,34 +899,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.001898734177215192</v>
+        <v>0.0001916932907348244</v>
       </c>
       <c r="C13" t="n">
-        <v>15.21089514978945</v>
+        <v>1.345579186327529</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9027476160939085</v>
+        <v>0.2678151261078595</v>
       </c>
       <c r="E13" t="n">
-        <v>2.568867352090828</v>
+        <v>0.5106784495120321</v>
       </c>
       <c r="F13" t="n">
-        <v>1.507870455596072</v>
+        <v>0.5895637637195452</v>
       </c>
       <c r="G13" t="n">
-        <v>3.222865628802278</v>
+        <v>0.6835070729540403</v>
       </c>
       <c r="H13" t="n">
-        <v>3625.483687986102</v>
+        <v>615.6481734316022</v>
       </c>
       <c r="I13" t="n">
-        <v>30.22558030151047</v>
+        <v>14.11770931778369</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1709292127899273</v>
+        <v>0.0478067642021828</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01570912190082644</v>
+        <v>0.004141184640522875</v>
       </c>
     </row>
     <row r="14">
@@ -936,34 +936,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.161730745636177</v>
+        <v>0.01632808805783768</v>
       </c>
       <c r="C14" t="n">
-        <v>0.03512405939925765</v>
+        <v>0.003107128331472791</v>
       </c>
       <c r="D14" t="n">
-        <v>1.448397597599252</v>
+        <v>0.4296912872877782</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7699464892828426</v>
+        <v>0.1530616514839386</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1626922951661343</v>
+        <v>0.06361122171360566</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2116513559021609</v>
+        <v>0.04488713319804218</v>
       </c>
       <c r="H14" t="n">
-        <v>2448.685457936379</v>
+        <v>415.8145117250455</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1318401253865034</v>
+        <v>0.06157964704266725</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3187832313446645</v>
+        <v>0.08915968501671086</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005357026280991738</v>
+        <v>0.0001412200827886711</v>
       </c>
     </row>
     <row r="15">
@@ -973,34 +973,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.2795952080932256</v>
+        <v>0.02822750343688795</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1473715755709655</v>
+        <v>0.01303671630050849</v>
       </c>
       <c r="D15" t="n">
-        <v>2.577682897723528</v>
+        <v>0.7647125929913133</v>
       </c>
       <c r="E15" t="n">
-        <v>1.464766837822778</v>
+        <v>0.2911885882418775</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3013305369084848</v>
+        <v>0.1178175252416959</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5931216419954455</v>
+        <v>0.125789556288967</v>
       </c>
       <c r="H15" t="n">
-        <v>8559.817442484878</v>
+        <v>1453.553905327621</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3857077246097432</v>
+        <v>0.1801556656099006</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6499605649782889</v>
+        <v>0.1817858455173652</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0008437395123966934</v>
+        <v>0.0002224237058823527</v>
       </c>
     </row>
     <row r="16">
@@ -1010,34 +1010,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04105763389057551</v>
+        <v>0.0041451157538089</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002324635776637229</v>
+        <v>0.0002056408571640626</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3456653215215163</v>
+        <v>0.1025473787180498</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7772999080269916</v>
+        <v>0.1545234756921127</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8078763176861072</v>
+        <v>0.3158723620502437</v>
       </c>
       <c r="G16" t="n">
-        <v>1.165061314458522</v>
+        <v>0.2470868291066395</v>
       </c>
       <c r="H16" t="n">
-        <v>38552.76753115416</v>
+        <v>6546.696373214857</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1426387226643356</v>
+        <v>0.06662343630618145</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02497551368369691</v>
+        <v>0.006985338983408978</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0001855989958677688</v>
+        <v>4.89269684095861e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1047,34 +1047,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4054441989539959</v>
+        <v>0.04093302455893377</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1535444173445698</v>
+        <v>0.01358277538048117</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1685849182948991</v>
+        <v>0.05001352576082006</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4148547417299164</v>
+        <v>0.08247112335594724</v>
       </c>
       <c r="F17" t="n">
-        <v>0.448510489231603</v>
+        <v>0.1753635606545187</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7638298190878012</v>
+        <v>0.1619934381421109</v>
       </c>
       <c r="H17" t="n">
-        <v>11494.16117442576</v>
+        <v>1951.838689996826</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7004337828129886</v>
+        <v>0.3271573430011284</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03205732440328302</v>
+        <v>0.008966032919043219</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001506970611570248</v>
+        <v>0.0003972624052287582</v>
       </c>
     </row>
     <row r="18">
@@ -1084,34 +1084,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.07899276445424373</v>
+        <v>0.007974988360236747</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01507641329760335</v>
+        <v>0.001333682714787989</v>
       </c>
       <c r="D18" t="n">
-        <v>1.741065518534593</v>
+        <v>0.5165161038319291</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7561306261807544</v>
+        <v>0.1503151244817162</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1165567488727017</v>
+        <v>0.0455726387484257</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2771577159735117</v>
+        <v>0.05877975721317431</v>
       </c>
       <c r="H18" t="n">
-        <v>2067.041189199701</v>
+        <v>351.006994392402</v>
       </c>
       <c r="I18" t="n">
-        <v>0.139468088302081</v>
+        <v>0.06514250214932592</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4137092746535727</v>
+        <v>0.1157093127546711</v>
       </c>
       <c r="K18" t="n">
-        <v>9.230948760330554e-05</v>
+        <v>2.433430936819166e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1121,34 +1121,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05796367491763566</v>
+        <v>0.005851923729703792</v>
       </c>
       <c r="C19" t="n">
-        <v>0.00496672234093126</v>
+        <v>0.0004393638993900729</v>
       </c>
       <c r="D19" t="n">
-        <v>1.669742702179072</v>
+        <v>0.4953570016464579</v>
       </c>
       <c r="E19" t="n">
-        <v>1.200600515053299</v>
+        <v>0.2386735963660172</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5371758861137952</v>
+        <v>0.2100309320480965</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8209029472007228</v>
+        <v>0.1740975377955895</v>
       </c>
       <c r="H19" t="n">
-        <v>20391.01375542614</v>
+        <v>3462.624977336514</v>
       </c>
       <c r="I19" t="n">
-        <v>0.156085216165822</v>
+        <v>0.07290400014329546</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3838674273045146</v>
+        <v>0.1073629210742314</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0002567560247933889</v>
+        <v>6.768513943355133e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1158,34 +1158,34 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.132602966963566</v>
+        <v>0.01338739219184884</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04194531703771719</v>
+        <v>0.003710547276413444</v>
       </c>
       <c r="D20" t="n">
-        <v>1.480724043948394</v>
+        <v>0.439281466371357</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7460272463111188</v>
+        <v>0.14830662125462</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1727596119305578</v>
+        <v>0.06754745187194783</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2393360329702269</v>
+        <v>0.05075851437489377</v>
       </c>
       <c r="H20" t="n">
-        <v>3370.320088758073</v>
+        <v>572.3185056381633</v>
       </c>
       <c r="I20" t="n">
-        <v>0.09812107781271379</v>
+        <v>0.04583021535696714</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3750018515686333</v>
+        <v>0.1048833303606021</v>
       </c>
       <c r="K20" t="n">
-        <v>0.000484021710743802</v>
+        <v>0.0001275961372549021</v>
       </c>
     </row>
     <row r="21">
@@ -1195,34 +1195,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3743988665298753</v>
+        <v>0.03779873540685003</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1140097662883779</v>
+        <v>0.01008547932551036</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4337219592038357</v>
+        <v>0.1286708478971379</v>
       </c>
       <c r="E21" t="n">
-        <v>0.754357044373004</v>
+        <v>0.1499625449657176</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5730600820211014</v>
+        <v>0.224061329366809</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8565821977336905</v>
+        <v>0.1816644124052659</v>
       </c>
       <c r="H21" t="n">
-        <v>12796.77945516727</v>
+        <v>2173.038020688782</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6729170247294856</v>
+        <v>0.3143048654600683</v>
       </c>
       <c r="J21" t="n">
-        <v>1.424581005586621e-05</v>
+        <v>3.984375000000082e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0.001104966330578511</v>
+        <v>0.0002912874204793026</v>
       </c>
     </row>
     <row r="22">
@@ -1232,34 +1232,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7286622275276908</v>
+        <v>0.07356462105391383</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2175924613564224</v>
+        <v>0.01924856388922198</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3945038028988812</v>
+        <v>0.1170361281933347</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7200584190931001</v>
+        <v>0.1431441435546524</v>
       </c>
       <c r="F22" t="n">
-        <v>0.404990467360418</v>
+        <v>0.1583476241751544</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8436432633793217</v>
+        <v>0.1789203162603125</v>
       </c>
       <c r="H22" t="n">
-        <v>13360.63270211038</v>
+        <v>2268.786685264026</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5821172631231198</v>
+        <v>0.271894277220058</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02306951635276305</v>
+        <v>0.006452255354913415</v>
       </c>
       <c r="K22" t="n">
-        <v>0.002868127520661157</v>
+        <v>0.0007560859041394336</v>
       </c>
     </row>
     <row r="23">
@@ -1269,34 +1269,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.06878598362487974</v>
+        <v>0.006944527420275399</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01674988254150189</v>
+        <v>0.001481720378671321</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2489336818453441</v>
+        <v>0.07385032561411875</v>
       </c>
       <c r="E23" t="n">
-        <v>0.407052504245752</v>
+        <v>0.08092007614523986</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3643733988044629</v>
+        <v>0.1424667162893125</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7257128599354418</v>
+        <v>0.153909572979597</v>
       </c>
       <c r="H23" t="n">
-        <v>12607.31625816877</v>
+        <v>2140.865024972055</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1555921175289274</v>
+        <v>0.07267368452482821</v>
       </c>
       <c r="J23" t="n">
-        <v>0.002841380126179341</v>
+        <v>0.0007946985040407844</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0001865357520661151</v>
+        <v>4.917391285403035e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1306,34 +1306,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1347798720640049</v>
+        <v>0.01360716919240433</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04505301383157609</v>
+        <v>0.003985458915870193</v>
       </c>
       <c r="D24" t="n">
-        <v>2.377500681082094</v>
+        <v>0.7053252020543546</v>
       </c>
       <c r="E24" t="n">
-        <v>1.331187075910427</v>
+        <v>0.2646335753315909</v>
       </c>
       <c r="F24" t="n">
-        <v>0.278969949464518</v>
+        <v>0.1090747369978386</v>
       </c>
       <c r="G24" t="n">
-        <v>0.406990987190168</v>
+        <v>0.08631486708194168</v>
       </c>
       <c r="H24" t="n">
-        <v>7240.178306302039</v>
+        <v>1229.464240692799</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1512599806373692</v>
+        <v>0.07065023786971769</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6014619265102621</v>
+        <v>0.1682213825708389</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0004101262809917364</v>
+        <v>0.0001081160784313728</v>
       </c>
     </row>
     <row r="25">
@@ -1343,34 +1343,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.169205963432866</v>
+        <v>0.1180412410366727</v>
       </c>
       <c r="C25" t="n">
-        <v>2.34520163926392</v>
+        <v>0.2074601450118083</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3007943498117058</v>
+        <v>0.08923565711080605</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8490305713969658</v>
+        <v>0.1687831858801197</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7216806015973306</v>
+        <v>0.2821706135975149</v>
       </c>
       <c r="G25" t="n">
-        <v>2.31368950099491</v>
+        <v>0.4906885116203969</v>
       </c>
       <c r="H25" t="n">
-        <v>4969.334200138099</v>
+        <v>843.8492037970357</v>
       </c>
       <c r="I25" t="n">
-        <v>7.656925830546943</v>
+        <v>3.576383052539416</v>
       </c>
       <c r="J25" t="n">
-        <v>0.06676081288393196</v>
+        <v>0.01867216485347472</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001855836636363636</v>
+        <v>0.0004892292657952068</v>
       </c>
     </row>
     <row r="26">
@@ -1380,34 +1380,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.310177258041349</v>
+        <v>0.2332319532080084</v>
       </c>
       <c r="C26" t="n">
-        <v>7.703849846205038</v>
+        <v>0.681494409471984</v>
       </c>
       <c r="D26" t="n">
-        <v>0.09869062651533525</v>
+        <v>0.02927821919954946</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4101678907032688</v>
+        <v>0.08153939995908355</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4193046549554182</v>
+        <v>0.1639443425681545</v>
       </c>
       <c r="G26" t="n">
-        <v>0.872283385821737</v>
+        <v>0.1849943288051469</v>
       </c>
       <c r="H26" t="n">
-        <v>2927.011305034719</v>
+        <v>497.0396555719335</v>
       </c>
       <c r="I26" t="n">
-        <v>1.534193744671522</v>
+        <v>0.7165884362971923</v>
       </c>
       <c r="J26" t="n">
-        <v>0.006513796315013132</v>
+        <v>0.001821827406855235</v>
       </c>
       <c r="K26" t="n">
-        <v>0.002884599876033057</v>
+        <v>0.0007604282897603484</v>
       </c>
     </row>
     <row r="27">
@@ -1417,34 +1417,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.00632911392405064</v>
+        <v>0.0006389776357827483</v>
       </c>
       <c r="C27" t="n">
-        <v>24.62034449149679</v>
+        <v>2.17795355117087</v>
       </c>
       <c r="D27" t="n">
-        <v>2.814358761716284</v>
+        <v>0.8349264326424976</v>
       </c>
       <c r="E27" t="n">
-        <v>1.823810991528643</v>
+        <v>0.3625648356653327</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4167795401371809</v>
+        <v>0.1629570454230058</v>
       </c>
       <c r="G27" t="n">
-        <v>0.545668049430227</v>
+        <v>0.1157255728992965</v>
       </c>
       <c r="H27" t="n">
-        <v>2884.59298201662</v>
+        <v>489.8365441160298</v>
       </c>
       <c r="I27" t="n">
-        <v>2.967505210407149</v>
+        <v>1.386056960416508</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7914094921466671</v>
+        <v>0.2213473423347709</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01444949366115703</v>
+        <v>0.003809125779956427</v>
       </c>
     </row>
     <row r="28">
@@ -1454,34 +1454,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2421559042367874</v>
+        <v>0.02444768873444883</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4705516665078754</v>
+        <v>0.04162572434492744</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1649256368298166</v>
+        <v>0.04892793892617891</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3227335524853907</v>
+        <v>0.06415787489167403</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3583776940952618</v>
+        <v>0.1401224497633726</v>
       </c>
       <c r="G28" t="n">
-        <v>0.695674768957212</v>
+        <v>0.1475390785171</v>
       </c>
       <c r="H28" t="n">
-        <v>6196.806652132889</v>
+        <v>1052.287922060302</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9975673260178599</v>
+        <v>0.4659419403416753</v>
       </c>
       <c r="J28" t="n">
-        <v>0.02471156641977192</v>
+        <v>0.006911516233029958</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001070809066115702</v>
+        <v>0.000282283</v>
       </c>
     </row>
     <row r="29">
@@ -1491,34 +1491,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.654355520648981</v>
+        <v>0.1670211963338907</v>
       </c>
       <c r="C29" t="n">
-        <v>9.298048061040349</v>
+        <v>0.822519636168954</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3363273231926426</v>
+        <v>0.09977710588048397</v>
       </c>
       <c r="E29" t="n">
-        <v>0.816333017178269</v>
+        <v>0.1622830696800173</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8755104639342298</v>
+        <v>0.3423167039166268</v>
       </c>
       <c r="G29" t="n">
-        <v>5.096574187841623</v>
+        <v>1.080884190173123</v>
       </c>
       <c r="H29" t="n">
-        <v>3681.579342099912</v>
+        <v>625.173850545268</v>
       </c>
       <c r="I29" t="n">
-        <v>5.471584486685432</v>
+        <v>2.555657774645253</v>
       </c>
       <c r="J29" t="n">
-        <v>0.1084045709906843</v>
+        <v>0.03031940344895702</v>
       </c>
       <c r="K29" t="n">
-        <v>0.002968076710743802</v>
+        <v>0.0007824341655773423</v>
       </c>
     </row>
     <row r="30">
@@ -1528,34 +1528,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1726981842996998</v>
+        <v>0.01743534384623167</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2340864308804535</v>
+        <v>0.0207076458086555</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3254091365239372</v>
+        <v>0.0965380438354347</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2810993164110862</v>
+        <v>0.05588118940702314</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3581987024225878</v>
+        <v>0.1400524656318947</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8623414794329484</v>
+        <v>0.1828858439602763</v>
       </c>
       <c r="H30" t="n">
-        <v>3604.261098269179</v>
+        <v>612.044337441936</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6832315186792013</v>
+        <v>0.3191225406176516</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01868376924817124</v>
+        <v>0.005225616711597894</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0001026293471074388</v>
+        <v>2.705479520697189e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1565,34 +1565,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.004746835443037943</v>
+        <v>0.0004792332268370575</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01079072541105597</v>
+        <v>0.0009545641709780282</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4134869524258416</v>
+        <v>0.122667795886333</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3500495537206944</v>
+        <v>0.06958816429387296</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3666060755761666</v>
+        <v>0.1433396727928435</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9477148736650215</v>
+        <v>0.2009918792470784</v>
       </c>
       <c r="H31" t="n">
-        <v>15471.88855515134</v>
+        <v>2627.301830120039</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1922129033957253</v>
+        <v>0.08977845487825029</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01014220047359492</v>
+        <v>0.002836646694958578</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0001469137768595048</v>
+        <v>3.872890413943372e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1602,34 +1602,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2276380408685902</v>
+        <v>0.02298198751261166</v>
       </c>
       <c r="C32" t="n">
-        <v>0.06443892488718508</v>
+        <v>0.005700366432327911</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6166741168729236</v>
+        <v>0.1829466546723006</v>
       </c>
       <c r="E32" t="n">
-        <v>1.031418574978258</v>
+        <v>0.20504104201375</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7041054648532623</v>
+        <v>0.2752988934651494</v>
       </c>
       <c r="G32" t="n">
-        <v>1.279366589840643</v>
+        <v>0.2713287532816396</v>
       </c>
       <c r="H32" t="n">
-        <v>24441.25447209688</v>
+        <v>4150.401702808905</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8687197929585714</v>
+        <v>0.4057600679045179</v>
       </c>
       <c r="J32" t="n">
-        <v>0.04989741398928718</v>
+        <v>0.01395568297512876</v>
       </c>
       <c r="K32" t="n">
-        <v>0.003348944099173554</v>
+        <v>0.0008828371154684096</v>
       </c>
     </row>
     <row r="33">
@@ -1639,34 +1639,34 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.41870308076339</v>
+        <v>0.1432300873869748</v>
       </c>
       <c r="C33" t="n">
-        <v>1.923092884885948</v>
+        <v>0.1701197552014493</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2640577991482584</v>
+        <v>0.07833714708065</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8624938500676727</v>
+        <v>0.1714596207965855</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2754165429130311</v>
+        <v>0.1076853870488788</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9067775978354705</v>
+        <v>0.1923098798094018</v>
       </c>
       <c r="H33" t="n">
-        <v>4059.206785470605</v>
+        <v>689.2992654572726</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9353507921978101</v>
+        <v>0.4368819543804586</v>
       </c>
       <c r="J33" t="n">
-        <v>1.284916201117053e-05</v>
+        <v>3.593749999999257e-06</v>
       </c>
       <c r="K33" t="n">
-        <v>0.003090520867768595</v>
+        <v>0.0008147124727668845</v>
       </c>
     </row>
     <row r="34">
@@ -1676,34 +1676,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.1026749343697529</v>
+        <v>0.0103659039172019</v>
       </c>
       <c r="C34" t="n">
-        <v>0.08638630614125122</v>
+        <v>0.007641865543264531</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3491977844631237</v>
+        <v>0.10359534272406</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4739439543607228</v>
+        <v>0.09421777405966177</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5996932151126194</v>
+        <v>0.2344746444674566</v>
       </c>
       <c r="G34" t="n">
-        <v>1.09250264716564</v>
+        <v>0.2316985479894915</v>
       </c>
       <c r="H34" t="n">
-        <v>20225.13841354553</v>
+        <v>3434.457466451128</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2107572767896381</v>
+        <v>0.0984401272247898</v>
       </c>
       <c r="J34" t="n">
-        <v>0.00376875402542964</v>
+        <v>0.001054073391487352</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0002567486570247936</v>
+        <v>6.768319716775604e-05</v>
       </c>
     </row>
     <row r="35">
@@ -1713,34 +1713,34 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.180587968047079</v>
+        <v>0.0182318843140182</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3458687327047335</v>
+        <v>0.03059608020080334</v>
       </c>
       <c r="D35" t="n">
-        <v>2.352317349646752</v>
+        <v>0.6978541470618698</v>
       </c>
       <c r="E35" t="n">
-        <v>1.442360687402404</v>
+        <v>0.286734353519755</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3334815987367917</v>
+        <v>0.1303883007673582</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4042252756591829</v>
+        <v>0.08572831349550457</v>
       </c>
       <c r="H35" t="n">
-        <v>6313.101526609911</v>
+        <v>1072.036108292249</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3569560157363684</v>
+        <v>0.1667263694900322</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6224975626647568</v>
+        <v>0.1741047870577991</v>
       </c>
       <c r="K35" t="n">
-        <v>0.004487677537190082</v>
+        <v>0.001183026104575163</v>
       </c>
     </row>
     <row r="36">
@@ -1750,34 +1750,34 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7385536523061119</v>
+        <v>0.0745632441305851</v>
       </c>
       <c r="C36" t="n">
-        <v>1.405328866036686</v>
+        <v>0.1243175535340146</v>
       </c>
       <c r="D36" t="n">
-        <v>0.331269402820422</v>
+        <v>0.09827658950339185</v>
       </c>
       <c r="E36" t="n">
-        <v>1.172061366669056</v>
+        <v>0.2330001512052944</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8994683774647193</v>
+        <v>0.3516840322699893</v>
       </c>
       <c r="G36" t="n">
-        <v>1.401667855095829</v>
+        <v>0.2972664712820685</v>
       </c>
       <c r="H36" t="n">
-        <v>28435.28721995214</v>
+        <v>4828.633678859798</v>
       </c>
       <c r="I36" t="n">
-        <v>1.024733107381171</v>
+        <v>0.4786304843117813</v>
       </c>
       <c r="J36" t="n">
-        <v>1.005586592178536e-05</v>
+        <v>2.812499999999343e-06</v>
       </c>
       <c r="K36" t="n">
-        <v>0.003287517801652891</v>
+        <v>0.0008666441263616555</v>
       </c>
     </row>
     <row r="37">
@@ -1787,34 +1787,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.1570864936411223</v>
+        <v>0.01585921149859254</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1740406351122147</v>
+        <v>0.01539590233684976</v>
       </c>
       <c r="D37" t="n">
-        <v>1.748731955078586</v>
+        <v>0.5187904800066473</v>
       </c>
       <c r="E37" t="n">
-        <v>1.024400534076992</v>
+        <v>0.2036458893044622</v>
       </c>
       <c r="F37" t="n">
-        <v>0.3044675154141472</v>
+        <v>0.1190440555763422</v>
       </c>
       <c r="G37" t="n">
-        <v>0.563294758099211</v>
+        <v>0.1194638547378193</v>
       </c>
       <c r="H37" t="n">
-        <v>10316.90249962138</v>
+        <v>1751.926839558347</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2351424464050086</v>
+        <v>0.1098299080945205</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3435352640931872</v>
+        <v>0.09608251917606328</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0001307317520661165</v>
+        <v>3.446305446623115e-05</v>
       </c>
     </row>
     <row r="38">
@@ -1824,34 +1824,34 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1225820326898951</v>
+        <v>0.01237569403514596</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2909961980664104</v>
+        <v>0.02574197136741322</v>
       </c>
       <c r="D38" t="n">
-        <v>2.923829407700766</v>
+        <v>0.8674027242845607</v>
       </c>
       <c r="E38" t="n">
-        <v>1.608254106877914</v>
+        <v>0.3197131658251275</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3020890754052016</v>
+        <v>0.118114106960232</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4071983737948047</v>
+        <v>0.08635884974440154</v>
       </c>
       <c r="H38" t="n">
-        <v>2340.739692841664</v>
+        <v>397.4840987844335</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3565823401745035</v>
+        <v>0.1665518337852105</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7806931385334852</v>
+        <v>0.2183501121835841</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0001512568181818184</v>
+        <v>3.987380174291945e-05</v>
       </c>
     </row>
     <row r="39">
@@ -1861,34 +1861,34 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.007911392405063262</v>
+        <v>0.0007987220447284317</v>
       </c>
       <c r="C39" t="n">
-        <v>23.06831827966916</v>
+        <v>2.040658924739964</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9755589833234108</v>
+        <v>0.2894158317192785</v>
       </c>
       <c r="E39" t="n">
-        <v>3.074894190602419</v>
+        <v>0.6112741463245772</v>
       </c>
       <c r="F39" t="n">
-        <v>1.023869348356419</v>
+        <v>0.4003236911591762</v>
       </c>
       <c r="G39" t="n">
-        <v>2.140636863096544</v>
+        <v>0.4539874152607436</v>
       </c>
       <c r="H39" t="n">
-        <v>3248.367527854212</v>
+        <v>551.6095802016587</v>
       </c>
       <c r="I39" t="n">
-        <v>2.364840339591002</v>
+        <v>1.104565343800735</v>
       </c>
       <c r="J39" t="n">
-        <v>0.08975964642051711</v>
+        <v>0.02510465110823838</v>
       </c>
       <c r="K39" t="n">
-        <v>0.003329501132231405</v>
+        <v>0.0008777116274509804</v>
       </c>
     </row>
     <row r="40">
@@ -1898,34 +1898,34 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7.246131051446693</v>
+        <v>0.7315582786764073</v>
       </c>
       <c r="C40" t="n">
-        <v>7.374223140388592</v>
+        <v>0.6523351239574523</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6419044735249365</v>
+        <v>0.1904316604790645</v>
       </c>
       <c r="E40" t="n">
-        <v>3.073967865997516</v>
+        <v>0.6110899974573374</v>
       </c>
       <c r="F40" t="n">
-        <v>1.618851376738617</v>
+        <v>0.6329563040581617</v>
       </c>
       <c r="G40" t="n">
-        <v>3.170368918386269</v>
+        <v>0.6723735424228597</v>
       </c>
       <c r="H40" t="n">
-        <v>20364.32451516564</v>
+        <v>3458.092842197939</v>
       </c>
       <c r="I40" t="n">
-        <v>5.446513334400088</v>
+        <v>2.54394758623214</v>
       </c>
       <c r="J40" t="n">
-        <v>0.08790231765611486</v>
+        <v>0.02458517946944462</v>
       </c>
       <c r="K40" t="n">
-        <v>0.003948668537190083</v>
+        <v>0.001040934407407407</v>
       </c>
     </row>
     <row r="41">
@@ -1935,34 +1935,34 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.002531645569620255</v>
+        <v>0.0002555910543130993</v>
       </c>
       <c r="C41" t="n">
-        <v>11.5293135759523</v>
+        <v>1.019900816334242</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9073352270133306</v>
+        <v>0.2691761173472881</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9310247058528104</v>
+        <v>0.1850832246574864</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7164369535127533</v>
+        <v>0.2801203944365179</v>
       </c>
       <c r="G41" t="n">
-        <v>1.220467926202672</v>
+        <v>0.2588374930738552</v>
       </c>
       <c r="H41" t="n">
-        <v>29348.70099290863</v>
+        <v>4983.741678041089</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5773053593474295</v>
+        <v>0.2696467419174208</v>
       </c>
       <c r="J41" t="n">
-        <v>0.06327863778223715</v>
+        <v>0.01769824400471945</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0001785654132231399</v>
+        <v>4.707279956427e-05</v>
       </c>
     </row>
     <row r="42">
@@ -1972,34 +1972,34 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7603237022687073</v>
+        <v>0.0767611149894286</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2650680979237204</v>
+        <v>0.02344833173940604</v>
       </c>
       <c r="D42" t="n">
-        <v>2.947953257711197</v>
+        <v>0.8745594664543218</v>
       </c>
       <c r="E42" t="n">
-        <v>1.897526298042895</v>
+        <v>0.3772190833458767</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3294173535953585</v>
+        <v>0.1287992175318789</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5023142848022465</v>
+        <v>0.1065310832198053</v>
       </c>
       <c r="H42" t="n">
-        <v>4030.628591929096</v>
+        <v>684.446364667205</v>
       </c>
       <c r="I42" t="n">
-        <v>9.970256295815775</v>
+        <v>4.65688925751066</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8254304746250353</v>
+        <v>0.2308625858716895</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0001563153057851241</v>
+        <v>4.120730283224406e-05</v>
       </c>
     </row>
     <row r="43">
@@ -2009,34 +2009,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.09678069262474319</v>
+        <v>0.009770830309718483</v>
       </c>
       <c r="C43" t="n">
-        <v>0.07252099602652638</v>
+        <v>0.006415318879269641</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3532577473868641</v>
+        <v>0.1047997983914363</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6446184346526117</v>
+        <v>0.1281470382140734</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4918409329610989</v>
+        <v>0.1923053737883936</v>
       </c>
       <c r="G43" t="n">
-        <v>1.30838641718896</v>
+        <v>0.2774832938467861</v>
       </c>
       <c r="H43" t="n">
-        <v>14342.09859060946</v>
+        <v>2435.450704065757</v>
       </c>
       <c r="I43" t="n">
-        <v>0.298684585061028</v>
+        <v>0.1395090551622497</v>
       </c>
       <c r="J43" t="n">
-        <v>0.008067516019611436</v>
+        <v>0.002256383386735073</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0002922218057851248</v>
+        <v>7.703450653594793e-05</v>
       </c>
     </row>
     <row r="44">
@@ -2046,34 +2046,34 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.06647045774653756</v>
+        <v>0.006710755478564176</v>
       </c>
       <c r="C44" t="n">
-        <v>0.05109167261211591</v>
+        <v>0.004519647961841023</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2801836014521282</v>
+        <v>0.0831211350974647</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3755075559663237</v>
+        <v>0.07464909245113664</v>
       </c>
       <c r="F44" t="n">
-        <v>0.262861010581071</v>
+        <v>0.1027762870199863</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4501826156919797</v>
+        <v>0.09547497084474202</v>
       </c>
       <c r="H44" t="n">
-        <v>4804.181638619383</v>
+        <v>815.8044291995178</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2666304604270537</v>
+        <v>0.1245372726686033</v>
       </c>
       <c r="J44" t="n">
-        <v>7.541899441340574e-06</v>
+        <v>2.109374999999942e-06</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0003844735041322309</v>
+        <v>0.0001013535816993463</v>
       </c>
     </row>
     <row r="45">
@@ -2083,34 +2083,34 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4159819206851544</v>
+        <v>0.04199689678482709</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1259607838245005</v>
+        <v>0.01114268472293659</v>
       </c>
       <c r="D45" t="n">
-        <v>3.998127500730942</v>
+        <v>1.18611115855018</v>
       </c>
       <c r="E45" t="n">
-        <v>2.466869704344535</v>
+        <v>0.4904018086949979</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5832358758994132</v>
+        <v>0.2280399730994102</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7904775707919901</v>
+        <v>0.1676449076310529</v>
       </c>
       <c r="H45" t="n">
-        <v>15945.95619324543</v>
+        <v>2707.803881871866</v>
       </c>
       <c r="I45" t="n">
-        <v>0.582872439914455</v>
+        <v>0.2722470038283565</v>
       </c>
       <c r="J45" t="n">
-        <v>1.108838235468468</v>
+        <v>0.310128193982587</v>
       </c>
       <c r="K45" t="n">
-        <v>0.002327767090909092</v>
+        <v>0.0006136379477124185</v>
       </c>
     </row>
     <row r="46">
@@ -2120,34 +2120,34 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1118923145887326</v>
+        <v>0.01129647648883051</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2314672592374032</v>
+        <v>0.02047594985561644</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3483874031058334</v>
+        <v>0.1033549295880639</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5050507775141471</v>
+        <v>0.1004016605901618</v>
       </c>
       <c r="F46" t="n">
-        <v>0.3140974621313463</v>
+        <v>0.1228092779864904</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5704654105332165</v>
+        <v>0.1209846105560379</v>
       </c>
       <c r="H46" t="n">
-        <v>3268.089129494727</v>
+        <v>554.958531423633</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3781049369995436</v>
+        <v>0.176604569339293</v>
       </c>
       <c r="J46" t="n">
-        <v>1.20111731843556e-05</v>
+        <v>3.359374999999456e-06</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0003414011157024785</v>
+        <v>8.999898692810435e-05</v>
       </c>
     </row>
     <row r="47">
@@ -2157,34 +2157,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1189386380754016</v>
+        <v>0.01200786250218112</v>
       </c>
       <c r="C47" t="n">
-        <v>0.07932014169599738</v>
+        <v>0.007016781765415153</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3131560636991313</v>
+        <v>0.09290296556407562</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7750516665064789</v>
+        <v>0.1540765361127338</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7811421469424675</v>
+        <v>0.3054195421378657</v>
       </c>
       <c r="G47" t="n">
-        <v>1.432889163567691</v>
+        <v>0.3038879031458995</v>
       </c>
       <c r="H47" t="n">
-        <v>25675.4029266941</v>
+        <v>4359.974081891451</v>
       </c>
       <c r="I47" t="n">
-        <v>0.300846863864252</v>
+        <v>0.1405190084304222</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01199463871082991</v>
+        <v>0.003354750514435241</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0007510373801652894</v>
+        <v>0.0001979858888888889</v>
       </c>
     </row>
     <row r="48">
@@ -2194,34 +2194,34 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.04829074207526798</v>
+        <v>0.004875359263828972</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1245497118115961</v>
+        <v>0.01101785912179504</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5331688036804165</v>
+        <v>0.1581734117585236</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7299518802756879</v>
+        <v>0.1451109159584199</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9961537307967975</v>
+        <v>0.3894871343836127</v>
       </c>
       <c r="G48" t="n">
-        <v>1.570044907598927</v>
+        <v>0.332975966980712</v>
       </c>
       <c r="H48" t="n">
-        <v>29254.36701258079</v>
+        <v>4967.722700249567</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3393959911355203</v>
+        <v>0.1585244649953973</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04842673499165067</v>
+        <v>0.0135443524429773</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0005092406694214873</v>
+        <v>0.0001342442723311546</v>
       </c>
     </row>
     <row r="49">
@@ -2231,34 +2231,34 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.1552000120777332</v>
+        <v>0.01566875521295965</v>
       </c>
       <c r="C49" t="n">
-        <v>0.07961622987717538</v>
+        <v>0.007042974181442437</v>
       </c>
       <c r="D49" t="n">
-        <v>0.09659511280947829</v>
+        <v>0.02865655013347856</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6504920286435609</v>
+        <v>0.129314680392997</v>
       </c>
       <c r="F49" t="n">
-        <v>1.019781309752105</v>
+        <v>0.3987253048940663</v>
       </c>
       <c r="G49" t="n">
-        <v>1.21244263426749</v>
+        <v>0.2571354848513602</v>
       </c>
       <c r="H49" t="n">
-        <v>26858.35247923304</v>
+        <v>4560.852307794288</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3322341194371379</v>
+        <v>0.155179310930515</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01913637313794075</v>
+        <v>0.005352204362017804</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0008243456363636367</v>
+        <v>0.0002173111590413944</v>
       </c>
     </row>
     <row r="50">
@@ -2268,34 +2268,34 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6390997202817003</v>
+        <v>0.06452252767061256</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3715810050440524</v>
+        <v>0.03287062736928156</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2191689702548608</v>
+        <v>0.06502012784227536</v>
       </c>
       <c r="E50" t="n">
-        <v>1.070840297221902</v>
+        <v>0.2128778904115829</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6765992354280574</v>
+        <v>0.264544205563763</v>
       </c>
       <c r="G50" t="n">
-        <v>1.348708726189848</v>
+        <v>0.2860348707892563</v>
       </c>
       <c r="H50" t="n">
-        <v>25240.29609021953</v>
+        <v>4286.088015320297</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9682441058656648</v>
+        <v>0.4522457037685306</v>
       </c>
       <c r="J50" t="n">
-        <v>0.007693118051643607</v>
+        <v>0.002151668955069071</v>
       </c>
       <c r="K50" t="n">
-        <v>0.004917806008264463</v>
+        <v>0.001296415091503268</v>
       </c>
     </row>
     <row r="51">
@@ -2305,34 +2305,34 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3261349140485525</v>
+        <v>0.03292608077934268</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4407398747875982</v>
+        <v>0.03898852738505676</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1906576706550374</v>
+        <v>0.05656177562766109</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5595015829314393</v>
+        <v>0.1112262182935994</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4140423118568247</v>
+        <v>0.1618868138251008</v>
       </c>
       <c r="G51" t="n">
-        <v>0.6336306700012212</v>
+        <v>0.1343807326982456</v>
       </c>
       <c r="H51" t="n">
-        <v>6835.450756586061</v>
+        <v>1160.736920929709</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8293963594078952</v>
+        <v>0.387392949764593</v>
       </c>
       <c r="J51" t="n">
-        <v>0.01042144591170671</v>
+        <v>0.00291474815343047</v>
       </c>
       <c r="K51" t="n">
-        <v>0.00181876796694215</v>
+        <v>0.0004794573507625275</v>
       </c>
     </row>
     <row r="52">
@@ -2342,34 +2342,34 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.629112792968372</v>
+        <v>0.1644727292581488</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3737216984278712</v>
+        <v>0.03305999639938861</v>
       </c>
       <c r="D52" t="n">
-        <v>0.3215744197517302</v>
+        <v>0.0954004111930133</v>
       </c>
       <c r="E52" t="n">
-        <v>1.362492660541008</v>
+        <v>0.270856974685863</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8968836148358735</v>
+        <v>0.3506734133682604</v>
       </c>
       <c r="G52" t="n">
-        <v>1.633902405221431</v>
+        <v>0.3465188993623975</v>
       </c>
       <c r="H52" t="n">
-        <v>32198.76124945301</v>
+        <v>5467.714174435416</v>
       </c>
       <c r="I52" t="n">
-        <v>1.186520018714913</v>
+        <v>0.5541976219100516</v>
       </c>
       <c r="J52" t="n">
-        <v>0.01609460233881113</v>
+        <v>0.004501459091636238</v>
       </c>
       <c r="K52" t="n">
-        <v>0.004950636801652892</v>
+        <v>0.001305069832244009</v>
       </c>
     </row>
     <row r="53">
@@ -2379,34 +2379,34 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8233473275922114</v>
+        <v>0.08312388355244052</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3785505099725759</v>
+        <v>0.03348716049757403</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2074579935558294</v>
+        <v>0.06154587142156273</v>
       </c>
       <c r="E53" t="n">
-        <v>1.116653587197825</v>
+        <v>0.2219853516718568</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7637791637950426</v>
+        <v>0.2986307721504941</v>
       </c>
       <c r="G53" t="n">
-        <v>1.40717968471686</v>
+        <v>0.2984354230674683</v>
       </c>
       <c r="H53" t="n">
-        <v>23207.18344951795</v>
+        <v>3940.842472559651</v>
       </c>
       <c r="I53" t="n">
-        <v>1.014090230758452</v>
+        <v>0.473659428769894</v>
       </c>
       <c r="J53" t="n">
-        <v>3.351955307259721e-06</v>
+        <v>9.374999999992032e-07</v>
       </c>
       <c r="K53" t="n">
-        <v>0.004501646198347108</v>
+        <v>0.001186708474945534</v>
       </c>
     </row>
     <row r="54">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.1754614112119533</v>
+        <v>0.01771431499775631</v>
       </c>
       <c r="C54" t="n">
-        <v>0.08069964600231481</v>
+        <v>0.00713881483866631</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7305234027825369</v>
+        <v>0.2167219428254859</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3991924780437651</v>
+        <v>0.07935754081592919</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2567650254968032</v>
+        <v>0.1003928117708222</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4856383839834414</v>
+        <v>0.1029944492206493</v>
       </c>
       <c r="H54" t="n">
-        <v>3963.656532251641</v>
+        <v>673.0737507597125</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3271301895973856</v>
+        <v>0.1527953766226472</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0003544247658566051</v>
+        <v>9.912817670051922e-05</v>
       </c>
       <c r="K54" t="n">
-        <v>2.115818181818861e-06</v>
+        <v>5.577647058825318e-07</v>
       </c>
     </row>
     <row r="55">
@@ -2453,34 +2453,34 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3891987037003354</v>
+        <v>0.03929290427134377</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3173038080216339</v>
+        <v>0.02806918301729839</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2090553170652463</v>
+        <v>0.06201974406268972</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4001648546196251</v>
+        <v>0.07955084459305799</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4079663329889466</v>
+        <v>0.1595111608263088</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7341600814597072</v>
+        <v>0.1557010642558842</v>
       </c>
       <c r="H55" t="n">
-        <v>10411.27218900165</v>
+        <v>1767.951881151223</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8484019488749744</v>
+        <v>0.3962700460794634</v>
       </c>
       <c r="J55" t="n">
-        <v>0.02389616787889082</v>
+        <v>0.006683459453627276</v>
       </c>
       <c r="K55" t="n">
-        <v>0.002385201272727273</v>
+        <v>0.0006287785490196081</v>
       </c>
     </row>
     <row r="56">
@@ -2490,34 +2490,34 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.236317113017252</v>
+        <v>0.02385821332698136</v>
       </c>
       <c r="C56" t="n">
-        <v>0.4290449609010861</v>
+        <v>0.0379539773104807</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3312553730040546</v>
+        <v>0.09827242732453617</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2923403346607898</v>
+        <v>0.0581158496614823</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2071188263987757</v>
+        <v>0.08098159518654832</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2997548152924447</v>
+        <v>0.06357216216940439</v>
       </c>
       <c r="H56" t="n">
-        <v>2594.698730617445</v>
+        <v>440.6092184067359</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6110826512225247</v>
+        <v>0.2854233782459117</v>
       </c>
       <c r="J56" t="n">
-        <v>9.776536312851188e-06</v>
+        <v>2.734375000000566e-06</v>
       </c>
       <c r="K56" t="n">
-        <v>0.0005911624297520663</v>
+        <v>0.0001558402047930284</v>
       </c>
     </row>
     <row r="57">
@@ -2527,34 +2527,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.064516941446568</v>
+        <v>0.2084304643760752</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4982569667940962</v>
+        <v>0.04407657783178543</v>
       </c>
       <c r="D57" t="n">
-        <v>0.4571543504625237</v>
+        <v>0.135622457303882</v>
       </c>
       <c r="E57" t="n">
-        <v>1.401825447450621</v>
+        <v>0.2786761431678946</v>
       </c>
       <c r="F57" t="n">
-        <v>1.011456675338321</v>
+        <v>0.3954704478349833</v>
       </c>
       <c r="G57" t="n">
-        <v>1.851600009362015</v>
+        <v>0.3926883241331521</v>
       </c>
       <c r="H57" t="n">
-        <v>36181.36689131656</v>
+        <v>6144.005698525453</v>
       </c>
       <c r="I57" t="n">
-        <v>1.164553265592128</v>
+        <v>0.5439374306366525</v>
       </c>
       <c r="J57" t="n">
-        <v>0.05192800665753157</v>
+        <v>0.01452361436202836</v>
       </c>
       <c r="K57" t="n">
-        <v>0.004008608904958677</v>
+        <v>0.001056735680827887</v>
       </c>
     </row>
     <row r="58">
@@ -2564,34 +2564,34 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.155802425367625</v>
+        <v>0.1166880403885526</v>
       </c>
       <c r="C58" t="n">
-        <v>2.828112651654608</v>
+        <v>0.2501791961079077</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4963911781306343</v>
+        <v>0.1472627161787548</v>
       </c>
       <c r="E58" t="n">
-        <v>3.396784380720789</v>
+        <v>0.6752643648420845</v>
       </c>
       <c r="F58" t="n">
-        <v>2.333458042464954</v>
+        <v>0.9123610724592702</v>
       </c>
       <c r="G58" t="n">
-        <v>6.096259817746281</v>
+        <v>1.292898055307265</v>
       </c>
       <c r="H58" t="n">
-        <v>932.7852170931085</v>
+        <v>158.3974896950561</v>
       </c>
       <c r="I58" t="n">
-        <v>3.826386836307369</v>
+        <v>1.787221835065376</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1082356493242376</v>
+        <v>0.03027215817037271</v>
       </c>
       <c r="K58" t="n">
-        <v>0.001561087710743802</v>
+        <v>0.000411528568627451</v>
       </c>
     </row>
     <row r="59">
@@ -2601,34 +2601,34 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7.970264037315345</v>
+        <v>0.8046656344382265</v>
       </c>
       <c r="C59" t="n">
-        <v>9.769359445850283</v>
+        <v>0.8642125663636788</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5613153652328524</v>
+        <v>0.1665235583524129</v>
       </c>
       <c r="E59" t="n">
-        <v>4.005485568806838</v>
+        <v>0.7962712275338895</v>
       </c>
       <c r="F59" t="n">
-        <v>2.268409446903376</v>
+        <v>0.8869276576180766</v>
       </c>
       <c r="G59" t="n">
-        <v>4.243420642927968</v>
+        <v>0.8999469282988175</v>
       </c>
       <c r="H59" t="n">
-        <v>18651.72755421621</v>
+        <v>3167.274490338602</v>
       </c>
       <c r="I59" t="n">
-        <v>4.516651863941591</v>
+        <v>2.109629574310167</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1025534356738381</v>
+        <v>0.02868291404002659</v>
       </c>
       <c r="K59" t="n">
-        <v>0.004697588668044077</v>
+        <v>0.001238362154320988</v>
       </c>
     </row>
     <row r="60">
@@ -2638,34 +2638,34 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.264693168404023</v>
+        <v>0.1276814828165084</v>
       </c>
       <c r="C60" t="n">
-        <v>1.298728622431744</v>
+        <v>0.1148875319843466</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1895126988301388</v>
+        <v>0.05622210065294118</v>
       </c>
       <c r="E60" t="n">
-        <v>2.268670050524442</v>
+        <v>0.451000672694618</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3768999332152376</v>
+        <v>0.147364478392264</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8992018675495573</v>
+        <v>0.1907032148628591</v>
       </c>
       <c r="H60" t="n">
-        <v>3595.328877371012</v>
+        <v>610.5275452139455</v>
       </c>
       <c r="I60" t="n">
-        <v>1.36118826222545</v>
+        <v>0.6357813488172368</v>
       </c>
       <c r="J60" t="n">
-        <v>0.02966387591635157</v>
+        <v>0.008296615295354578</v>
       </c>
       <c r="K60" t="n">
-        <v>0.001261216363636364</v>
+        <v>0.0003324775163398693</v>
       </c>
     </row>
     <row r="61">
@@ -2675,34 +2675,34 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6884405951563395</v>
+        <v>0.06950390673143875</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7390806836819087</v>
+        <v>0.06538021432570731</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3574664147727354</v>
+        <v>0.1060483697159115</v>
       </c>
       <c r="E61" t="n">
-        <v>1.117807344790625</v>
+        <v>0.2222147131210279</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4917744945330489</v>
+        <v>0.1922793969615705</v>
       </c>
       <c r="G61" t="n">
-        <v>1.182800391529257</v>
+        <v>0.2508489420961377</v>
       </c>
       <c r="H61" t="n">
-        <v>11305.78679037246</v>
+        <v>1919.850587044379</v>
       </c>
       <c r="I61" t="n">
-        <v>0.785779114964648</v>
+        <v>0.3670202862077677</v>
       </c>
       <c r="J61" t="n">
-        <v>0.03070764653063179</v>
+        <v>0.008588544889036077</v>
       </c>
       <c r="K61" t="n">
-        <v>0.002010068148760332</v>
+        <v>0.0005298872461873641</v>
       </c>
     </row>
     <row r="62">
@@ -2712,34 +2712,34 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4.787114605290146</v>
+        <v>0.4832997492880786</v>
       </c>
       <c r="C62" t="n">
-        <v>8.106542749883792</v>
+        <v>0.7171172432589507</v>
       </c>
       <c r="D62" t="n">
-        <v>0.40053685414262</v>
+        <v>0.1188259333956439</v>
       </c>
       <c r="E62" t="n">
-        <v>3.259207593879735</v>
+        <v>0.6479147626387425</v>
       </c>
       <c r="F62" t="n">
-        <v>1.792118919879977</v>
+        <v>0.7007023524575767</v>
       </c>
       <c r="G62" t="n">
-        <v>3.514558049704956</v>
+        <v>0.7453693581924604</v>
       </c>
       <c r="H62" t="n">
-        <v>7546.7842428155</v>
+        <v>1281.529399723387</v>
       </c>
       <c r="I62" t="n">
-        <v>3.787531331656711</v>
+        <v>1.769073276308793</v>
       </c>
       <c r="J62" t="n">
-        <v>0.08343375552741303</v>
+        <v>0.02333537849907333</v>
       </c>
       <c r="K62" t="n">
-        <v>0.003509826677685951</v>
+        <v>0.0009252484270152506</v>
       </c>
     </row>
     <row r="63">
@@ -2749,34 +2749,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8968941213124617</v>
+        <v>0.09054905505902169</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9726280271155052</v>
+        <v>0.08604017162944853</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4596003679280003</v>
+        <v>0.1363481091519734</v>
       </c>
       <c r="E63" t="n">
-        <v>3.337315389547369</v>
+        <v>0.6634422159943564</v>
       </c>
       <c r="F63" t="n">
-        <v>1.460693790832026</v>
+        <v>0.571118112811801</v>
       </c>
       <c r="G63" t="n">
-        <v>3.128508367449928</v>
+        <v>0.663495734304817</v>
       </c>
       <c r="H63" t="n">
-        <v>3952.321819047834</v>
+        <v>671.1489881401982</v>
       </c>
       <c r="I63" t="n">
-        <v>3.572103871938814</v>
+        <v>1.66845180849817</v>
       </c>
       <c r="J63" t="n">
-        <v>0.09060507063999665</v>
+        <v>0.02534110569462406</v>
       </c>
       <c r="K63" t="n">
-        <v>0.003387769214876034</v>
+        <v>0.0008930720588235297</v>
       </c>
     </row>
     <row r="64">
@@ -2786,34 +2786,34 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7563487933688958</v>
+        <v>0.07635981428261057</v>
       </c>
       <c r="C64" t="n">
-        <v>0.3922801640234932</v>
+        <v>0.03470170681746285</v>
       </c>
       <c r="D64" t="n">
-        <v>4.547351986391244</v>
+        <v>1.349047755962736</v>
       </c>
       <c r="E64" t="n">
-        <v>3.179382414971568</v>
+        <v>0.6320459017714563</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8187562431804438</v>
+        <v>0.3201263149011825</v>
       </c>
       <c r="G64" t="n">
-        <v>1.209577027549841</v>
+        <v>0.2565277454401004</v>
       </c>
       <c r="H64" t="n">
-        <v>24258.78204367788</v>
+        <v>4119.415818737753</v>
       </c>
       <c r="I64" t="n">
-        <v>1.08756716583378</v>
+        <v>0.5079789025602223</v>
       </c>
       <c r="J64" t="n">
-        <v>1.297871091508629</v>
+        <v>0.3629983209063197</v>
       </c>
       <c r="K64" t="n">
-        <v>0.003241588652892562</v>
+        <v>0.0008545364422657952</v>
       </c>
     </row>
     <row r="65">
@@ -2823,34 +2823,34 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.04728268680512238</v>
+        <v>0.004773587549654527</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0118163057719713</v>
+        <v>0.001045288587520538</v>
       </c>
       <c r="D65" t="n">
-        <v>2.897354518344827</v>
+        <v>0.8595485071089651</v>
       </c>
       <c r="E65" t="n">
-        <v>1.794508653354812</v>
+        <v>0.3567396720524627</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4367054514172189</v>
+        <v>0.1707478972207865</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9012474099849931</v>
+        <v>0.1911370346008442</v>
       </c>
       <c r="H65" t="n">
-        <v>12068.30834943156</v>
+        <v>2049.335380092151</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3000242686717282</v>
+        <v>0.140134792157371</v>
       </c>
       <c r="J65" t="n">
-        <v>0.7310192550501978</v>
+        <v>0.2044569478968522</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0005597221735537199</v>
+        <v>0.0001475520326797388</v>
       </c>
     </row>
     <row r="66">
@@ -2860,34 +2860,34 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.3299289068024879</v>
+        <v>0.03330911646951636</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1818018167902987</v>
+        <v>0.01608246840837257</v>
       </c>
       <c r="D66" t="n">
-        <v>3.309269190589927</v>
+        <v>0.9817498598750115</v>
       </c>
       <c r="E66" t="n">
-        <v>2.009360229454789</v>
+        <v>0.3994511299518556</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3067024442671821</v>
+        <v>0.1199178926233847</v>
       </c>
       <c r="G66" t="n">
-        <v>0.534407318178362</v>
+        <v>0.1133373909693707</v>
       </c>
       <c r="H66" t="n">
-        <v>4735.150012068078</v>
+        <v>804.0820775209944</v>
       </c>
       <c r="I66" t="n">
-        <v>0.6285009675732744</v>
+        <v>0.2935590939076816</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8342501550312571</v>
+        <v>0.2333293402353047</v>
       </c>
       <c r="K66" t="n">
-        <v>0.0009307814214876034</v>
+        <v>0.000245369394335512</v>
       </c>
     </row>
     <row r="67">
@@ -2897,34 +2897,34 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.576937048121499</v>
+        <v>0.05824667961865614</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4665539406590751</v>
+        <v>0.04127207936599511</v>
       </c>
       <c r="D67" t="n">
-        <v>4.186637154612255</v>
+        <v>1.242035689201636</v>
       </c>
       <c r="E67" t="n">
-        <v>3.034938098938377</v>
+        <v>0.6033310678612436</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6975504032847643</v>
+        <v>0.2727359234464754</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9923002849305967</v>
+        <v>0.2104475772067574</v>
       </c>
       <c r="H67" t="n">
-        <v>20235.67105038261</v>
+        <v>3436.246027423461</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8907922294188176</v>
+        <v>0.4160696215598181</v>
       </c>
       <c r="J67" t="n">
-        <v>1.105766276347999</v>
+        <v>0.3092690054160809</v>
       </c>
       <c r="K67" t="n">
-        <v>0.002855560404958678</v>
+        <v>0.0007527730043572985</v>
       </c>
     </row>
     <row r="68">
@@ -2934,34 +2934,34 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5017859350782804</v>
+        <v>0.05065953849352607</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7177575815608371</v>
+        <v>0.06349393990730483</v>
       </c>
       <c r="D68" t="n">
-        <v>2.830335456790812</v>
+        <v>0.8396661855146075</v>
       </c>
       <c r="E68" t="n">
-        <v>1.937297049789423</v>
+        <v>0.385125317126813</v>
       </c>
       <c r="F68" t="n">
-        <v>0.464400855966223</v>
+        <v>0.181576550891298</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6634779933631635</v>
+        <v>0.1407107690622548</v>
       </c>
       <c r="H68" t="n">
-        <v>9546.532978594772</v>
+        <v>1621.109373723641</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7346694846728938</v>
+        <v>0.3431480926352817</v>
       </c>
       <c r="J68" t="n">
-        <v>0.7940536291625978</v>
+        <v>0.2220868744064141</v>
       </c>
       <c r="K68" t="n">
-        <v>0.002473137305785125</v>
+        <v>0.0006519599433551201</v>
       </c>
     </row>
     <row r="69">
@@ -2971,34 +2971,34 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4.089634321506623</v>
+        <v>0.4128832094556207</v>
       </c>
       <c r="C69" t="n">
-        <v>6.841481094549961</v>
+        <v>0.6052079429794196</v>
       </c>
       <c r="D69" t="n">
-        <v>2.841067569280491</v>
+        <v>0.8428500455532124</v>
       </c>
       <c r="E69" t="n">
-        <v>1.823737328002536</v>
+        <v>0.3625501917113476</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4276932892638608</v>
+        <v>0.1672242230094735</v>
       </c>
       <c r="G69" t="n">
-        <v>0.5901583160050214</v>
+        <v>0.1251610925218703</v>
       </c>
       <c r="H69" t="n">
-        <v>7697.978647417061</v>
+        <v>1307.203921259501</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6381592503189506</v>
+        <v>0.2980702671242835</v>
       </c>
       <c r="J69" t="n">
-        <v>0.7242461695307887</v>
+        <v>0.2025626005406424</v>
       </c>
       <c r="K69" t="n">
-        <v>0.002325255595041321</v>
+        <v>0.0006129758758169932</v>
       </c>
     </row>
     <row r="70">
@@ -3008,34 +3008,34 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>8.019653069880757</v>
+        <v>0.8096518754256611</v>
       </c>
       <c r="C70" t="n">
-        <v>2.249336865133107</v>
+        <v>0.1989797996079287</v>
       </c>
       <c r="D70" t="n">
-        <v>0.7392753049959307</v>
+        <v>0.2193183404821261</v>
       </c>
       <c r="E70" t="n">
-        <v>1.321597439460669</v>
+        <v>0.2627272018204944</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9794365784366517</v>
+        <v>0.3829508784157719</v>
       </c>
       <c r="G70" t="n">
-        <v>1.613243546770548</v>
+        <v>0.3421375575701297</v>
       </c>
       <c r="H70" t="n">
-        <v>32178.02407092376</v>
+        <v>5464.192766760639</v>
       </c>
       <c r="I70" t="n">
-        <v>1.248112650351372</v>
+        <v>0.5829661967690564</v>
       </c>
       <c r="J70" t="n">
-        <v>0.07955167374486936</v>
+        <v>0.02224960875051815</v>
       </c>
       <c r="K70" t="n">
-        <v>0.004062942487603305</v>
+        <v>0.00107105891285403</v>
       </c>
     </row>
     <row r="71">
@@ -3045,34 +3045,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.552920758604977</v>
+        <v>0.1567804983128347</v>
       </c>
       <c r="C71" t="n">
-        <v>0.1597697616500802</v>
+        <v>0.0141334789151994</v>
       </c>
       <c r="D71" t="n">
-        <v>5.132613452404446</v>
+        <v>1.522675324213319</v>
       </c>
       <c r="E71" t="n">
-        <v>3.374517686020229</v>
+        <v>0.6708378532449852</v>
       </c>
       <c r="F71" t="n">
-        <v>0.8881007298602241</v>
+        <v>0.3472393844678714</v>
       </c>
       <c r="G71" t="n">
-        <v>1.097799249525955</v>
+        <v>0.2328218542618803</v>
       </c>
       <c r="H71" t="n">
-        <v>28609.64086553689</v>
+        <v>4858.240901694944</v>
       </c>
       <c r="I71" t="n">
-        <v>0.6991797589305816</v>
+        <v>0.3265716157967942</v>
       </c>
       <c r="J71" t="n">
-        <v>1.47465725293255</v>
+        <v>0.4124432004295724</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0008597231570247934</v>
+        <v>0.0002266372592592593</v>
       </c>
     </row>
     <row r="72">
@@ -3082,34 +3082,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2751523014688836</v>
+        <v>0.02777895439749752</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2446432673610592</v>
+        <v>0.02164151980501677</v>
       </c>
       <c r="D72" t="n">
-        <v>3.592246317383149</v>
+        <v>1.065699740823667</v>
       </c>
       <c r="E72" t="n">
-        <v>2.082618389552782</v>
+        <v>0.4140144991279626</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4311863574045685</v>
+        <v>0.1685899811834078</v>
       </c>
       <c r="G72" t="n">
-        <v>0.6263392515177462</v>
+        <v>0.1328343647514146</v>
       </c>
       <c r="H72" t="n">
-        <v>13335.65929041911</v>
+        <v>2264.545917240981</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4789167534263476</v>
+        <v>0.2236915700160101</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9053873468799768</v>
+        <v>0.2532255235804935</v>
       </c>
       <c r="K72" t="n">
-        <v>0.001102828479338843</v>
+        <v>0.0002907238474945533</v>
       </c>
     </row>
     <row r="73">
@@ -3119,34 +3119,34 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.07622927392367082</v>
+        <v>0.007695990594210856</v>
       </c>
       <c r="C73" t="n">
-        <v>0.02205184050957095</v>
+        <v>0.001950739737385123</v>
       </c>
       <c r="D73" t="n">
-        <v>3.948801696171347</v>
+        <v>1.171477836530833</v>
       </c>
       <c r="E73" t="n">
-        <v>2.680078970269653</v>
+        <v>0.5327867832463766</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6541475039308476</v>
+        <v>0.2557657808162053</v>
       </c>
       <c r="G73" t="n">
-        <v>1.222254401525954</v>
+        <v>0.2592163697195983</v>
       </c>
       <c r="H73" t="n">
-        <v>20148.80404352891</v>
+        <v>3421.495026259626</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3495538512679239</v>
+        <v>0.1632689799132072</v>
       </c>
       <c r="J73" t="n">
-        <v>1.128327713500423</v>
+        <v>0.3155791573696497</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0006400429049586783</v>
+        <v>0.0001687259074074076</v>
       </c>
     </row>
     <row r="74">
@@ -3156,34 +3156,34 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.3435011655231749</v>
+        <v>0.03467935089626942</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2618270622600231</v>
+        <v>0.02316162473838666</v>
       </c>
       <c r="D74" t="n">
-        <v>2.680706809891054</v>
+        <v>0.7952763536010128</v>
       </c>
       <c r="E74" t="n">
-        <v>1.625438851653077</v>
+        <v>0.3231294102683827</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3597417488998403</v>
+        <v>0.1406557829031808</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5794394954158595</v>
+        <v>0.1228878392962494</v>
       </c>
       <c r="H74" t="n">
-        <v>10329.84916034926</v>
+        <v>1754.125329115912</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4367814554792501</v>
+        <v>0.2040110913452464</v>
       </c>
       <c r="J74" t="n">
-        <v>0.7109408460262803</v>
+        <v>0.1988412678729752</v>
       </c>
       <c r="K74" t="n">
-        <v>0.001671278037190083</v>
+        <v>0.0004405765631808281</v>
       </c>
     </row>
     <row r="75">
@@ -3193,34 +3193,34 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4116459244404361</v>
+        <v>0.04155914125341144</v>
       </c>
       <c r="C75" t="n">
-        <v>0.5277996356288788</v>
+        <v>0.04668996776717004</v>
       </c>
       <c r="D75" t="n">
-        <v>3.417359403477303</v>
+        <v>1.0138166230316</v>
       </c>
       <c r="E75" t="n">
-        <v>2.267558683446131</v>
+        <v>0.4507797382754357</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5170650244137616</v>
+        <v>0.2021677663023176</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7771885631635038</v>
+        <v>0.1648265677581659</v>
       </c>
       <c r="H75" t="n">
-        <v>12550.89301075441</v>
+        <v>2131.283718807353</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8420063004533013</v>
+        <v>0.3932827781952662</v>
       </c>
       <c r="J75" t="n">
-        <v>0.9026773417655519</v>
+        <v>0.2524675690250528</v>
       </c>
       <c r="K75" t="n">
-        <v>0.002265209380165288</v>
+        <v>0.000597146699346405</v>
       </c>
     </row>
     <row r="76">
@@ -3230,34 +3230,34 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.2667687441195301</v>
+        <v>0.02693256330408035</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1352855000828321</v>
+        <v>0.01196756346886591</v>
       </c>
       <c r="D76" t="n">
-        <v>0.6442937575431296</v>
+        <v>0.1911404814044617</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2300534296961972</v>
+        <v>0.04573351313237654</v>
       </c>
       <c r="F76" t="n">
-        <v>0.228246453290804</v>
+        <v>0.08924230696235037</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5634706108129477</v>
+        <v>0.1195011496757661</v>
       </c>
       <c r="H76" t="n">
-        <v>5328.666027044595</v>
+        <v>904.8678159132331</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2956977027675037</v>
+        <v>0.1381139475889369</v>
       </c>
       <c r="J76" t="n">
-        <v>0.003621122941919844</v>
+        <v>0.001012782822818206</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0005828205123966948</v>
+        <v>0.0001536411372549021</v>
       </c>
     </row>
     <row r="77">
@@ -3267,34 +3267,34 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8580683162988474</v>
+        <v>0.08662926132601782</v>
       </c>
       <c r="C77" t="n">
-        <v>0.932628819289306</v>
+        <v>0.08250178016790014</v>
       </c>
       <c r="D77" t="n">
-        <v>2.574739264637528</v>
+        <v>0.7638393151757999</v>
       </c>
       <c r="E77" t="n">
-        <v>1.794319823166787</v>
+        <v>0.3567021335211082</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3921269323737573</v>
+        <v>0.1533180978830727</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4058543800060866</v>
+        <v>0.08607381482008282</v>
       </c>
       <c r="H77" t="n">
-        <v>4537.227311510729</v>
+        <v>770.4725623320105</v>
       </c>
       <c r="I77" t="n">
-        <v>0.307870665425801</v>
+        <v>0.143799672945796</v>
       </c>
       <c r="J77" t="n">
-        <v>0.7572662577840658</v>
+        <v>0.2117979064739809</v>
       </c>
       <c r="K77" t="n">
-        <v>0.0004741567520661161</v>
+        <v>0.0001249955708061003</v>
       </c>
     </row>
     <row r="78">
@@ -3304,34 +3304,34 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.3696802379530617</v>
+        <v>0.03732234990197045</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2531189164391244</v>
+        <v>0.02239128876192254</v>
       </c>
       <c r="D78" t="n">
-        <v>4.620269845266614</v>
+        <v>1.370680054095762</v>
       </c>
       <c r="E78" t="n">
-        <v>2.766448760539746</v>
+        <v>0.5499566813121182</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6692378086900445</v>
+        <v>0.2616659540283597</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9965778415128218</v>
+        <v>0.2113547637033904</v>
       </c>
       <c r="H78" t="n">
-        <v>23108.18237913066</v>
+        <v>3924.030970041055</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6241173567971371</v>
+        <v>0.2915116049237657</v>
       </c>
       <c r="J78" t="n">
-        <v>1.195384000998852</v>
+        <v>0.3343339627793664</v>
       </c>
       <c r="K78" t="n">
-        <v>0.002968327495867768</v>
+        <v>0.0007825002766884528</v>
       </c>
     </row>
     <row r="79">
@@ -3341,34 +3341,34 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.04358010704833899</v>
+        <v>0.004399780775487258</v>
       </c>
       <c r="C79" t="n">
-        <v>0.004209153219825265</v>
+        <v>0.0003723481694460811</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3967721202074618</v>
+        <v>0.1177090623282137</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8595873088884939</v>
+        <v>0.1708818144175921</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8817056958399638</v>
+        <v>0.3447389837788687</v>
       </c>
       <c r="G79" t="n">
-        <v>1.501832194488101</v>
+        <v>0.3185093781598926</v>
       </c>
       <c r="H79" t="n">
-        <v>28076.33230941586</v>
+        <v>4767.67907141024</v>
       </c>
       <c r="I79" t="n">
-        <v>0.422464668188595</v>
+        <v>0.1973240322609281</v>
       </c>
       <c r="J79" t="n">
-        <v>0.04924634095600514</v>
+        <v>0.01377358598613269</v>
       </c>
       <c r="K79" t="n">
-        <v>0.0006607779834710744</v>
+        <v>0.0001741920174291939</v>
       </c>
     </row>
     <row r="80">
@@ -3378,34 +3378,34 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.267699712558069</v>
+        <v>0.02702655244995201</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2159149820678749</v>
+        <v>0.0191001714906197</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3233352364969543</v>
+        <v>0.09592278682742979</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8603472876662287</v>
+        <v>0.1710328945360575</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4278074322487961</v>
+        <v>0.167268851888268</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8932417870501986</v>
+        <v>0.1894391977905119</v>
       </c>
       <c r="H80" t="n">
-        <v>16853.42145335599</v>
+        <v>2861.901756230263</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4307710448042688</v>
+        <v>0.2012037596102243</v>
       </c>
       <c r="J80" t="n">
-        <v>8.659217877095881e-06</v>
+        <v>2.421875000000254e-06</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0003195185619834715</v>
+        <v>8.423038344226591e-05</v>
       </c>
     </row>
     <row r="81">
@@ -3415,34 +3415,34 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2.899266800857824</v>
+        <v>0.2927055300546557</v>
       </c>
       <c r="C81" t="n">
-        <v>5.996143301637492</v>
+        <v>0.5304280612987011</v>
       </c>
       <c r="D81" t="n">
-        <v>3.18286753754297</v>
+        <v>0.9442507028044143</v>
       </c>
       <c r="E81" t="n">
-        <v>2.561657468116171</v>
+        <v>0.5092451593242989</v>
       </c>
       <c r="F81" t="n">
-        <v>0.5796751677195409</v>
+        <v>0.2266477682795322</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8484902976243667</v>
+        <v>0.1799482778854362</v>
       </c>
       <c r="H81" t="n">
-        <v>11785.76977203171</v>
+        <v>2001.357131099724</v>
       </c>
       <c r="I81" t="n">
-        <v>0.6695097103924401</v>
+        <v>0.3127133832491438</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8732343399512383</v>
+        <v>0.244232729455112</v>
       </c>
       <c r="K81" t="n">
-        <v>0.001474605214876032</v>
+        <v>0.000388730350762527</v>
       </c>
     </row>
     <row r="82">
@@ -3452,34 +3452,34 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.005658397083184</v>
+        <v>0.1015297295457783</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9784583151111879</v>
+        <v>0.08655592787522046</v>
       </c>
       <c r="D82" t="n">
-        <v>3.748091172969394</v>
+        <v>1.111933714647587</v>
       </c>
       <c r="E82" t="n">
-        <v>2.462157179426663</v>
+        <v>0.4894649814522883</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4880579555237802</v>
+        <v>0.1908262636912798</v>
       </c>
       <c r="G82" t="n">
-        <v>1.016699166165069</v>
+        <v>0.2156221050390348</v>
       </c>
       <c r="H82" t="n">
-        <v>11211.40693192242</v>
+        <v>1903.823818628335</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6429241742134507</v>
+        <v>0.3002958591490809</v>
       </c>
       <c r="J82" t="n">
-        <v>0.9974519744263599</v>
+        <v>0.2789748490973725</v>
       </c>
       <c r="K82" t="n">
-        <v>0.001811480239669421</v>
+        <v>0.0004775361851851852</v>
       </c>
     </row>
     <row r="83">
@@ -3489,34 +3489,34 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3.274234437050639</v>
+        <v>0.3305616875744415</v>
       </c>
       <c r="C83" t="n">
-        <v>3.500792545363915</v>
+        <v>0.3096854943975771</v>
       </c>
       <c r="D83" t="n">
-        <v>5.733908618420454</v>
+        <v>1.701059556798068</v>
       </c>
       <c r="E83" t="n">
-        <v>5.01123644542922</v>
+        <v>0.9962096548142425</v>
       </c>
       <c r="F83" t="n">
-        <v>1.265907955609146</v>
+        <v>0.4949586060669995</v>
       </c>
       <c r="G83" t="n">
-        <v>1.819501715607733</v>
+        <v>0.3858809007597608</v>
       </c>
       <c r="H83" t="n">
-        <v>16571.96238199819</v>
+        <v>2814.106819584599</v>
       </c>
       <c r="I83" t="n">
-        <v>1.956194712209557</v>
+        <v>0.9136958840978794</v>
       </c>
       <c r="J83" t="n">
-        <v>1.624422201209874</v>
+        <v>0.4543305844008866</v>
       </c>
       <c r="K83" t="n">
-        <v>0.003624378958677687</v>
+        <v>0.0009554463050108935</v>
       </c>
     </row>
     <row r="84">
@@ -3526,34 +3526,34 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4255626359784266</v>
+        <v>0.04296415110836511</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4599641444990627</v>
+        <v>0.04068913585953247</v>
       </c>
       <c r="D84" t="n">
-        <v>1.763504826096075</v>
+        <v>0.5231730984085021</v>
       </c>
       <c r="E84" t="n">
-        <v>1.140945080629005</v>
+        <v>0.2268143834985371</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2827079417582148</v>
+        <v>0.1105362583090678</v>
       </c>
       <c r="G84" t="n">
-        <v>0.354848729641655</v>
+        <v>0.07525650910521006</v>
       </c>
       <c r="H84" t="n">
-        <v>4960.295891140741</v>
+        <v>842.3143966088051</v>
       </c>
       <c r="I84" t="n">
-        <v>0.229800527409324</v>
+        <v>0.1073348142426266</v>
       </c>
       <c r="J84" t="n">
-        <v>0.4728582826877363</v>
+        <v>0.1322525509392262</v>
       </c>
       <c r="K84" t="n">
-        <v>0.0004900432396694214</v>
+        <v>0.0001291835119825708</v>
       </c>
     </row>
     <row r="85">
@@ -3563,34 +3563,34 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.801367039564033</v>
+        <v>0.1818632538345797</v>
       </c>
       <c r="C85" t="n">
-        <v>1.250822519182895</v>
+        <v>0.1106496843892561</v>
       </c>
       <c r="D85" t="n">
-        <v>2.089328818534153</v>
+        <v>0.6198342161651321</v>
       </c>
       <c r="E85" t="n">
-        <v>1.51769463848148</v>
+        <v>0.3017103799390893</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3683927313609717</v>
+        <v>0.1440382391087042</v>
       </c>
       <c r="G85" t="n">
-        <v>0.4960751372861336</v>
+        <v>0.1052078814647102</v>
       </c>
       <c r="H85" t="n">
-        <v>5145.072387636593</v>
+        <v>873.6915375231948</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6405663526785634</v>
+        <v>0.2991945721358722</v>
       </c>
       <c r="J85" t="n">
-        <v>0.5649805924229025</v>
+        <v>0.1580180094432805</v>
       </c>
       <c r="K85" t="n">
-        <v>0.0006168824793388432</v>
+        <v>0.0001626204357298475</v>
       </c>
     </row>
     <row r="86">
@@ -3600,34 +3600,34 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.3627440941379288</v>
+        <v>0.03662208745929249</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2967697919444666</v>
+        <v>0.02625271236431819</v>
       </c>
       <c r="D86" t="n">
-        <v>0.5066393289783884</v>
+        <v>0.1503030009302552</v>
       </c>
       <c r="E86" t="n">
-        <v>0.3477935462087227</v>
+        <v>0.06913968087281835</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1964679059201006</v>
+        <v>0.07681718123362492</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4070557537002358</v>
+        <v>0.08632860279817081</v>
       </c>
       <c r="H86" t="n">
-        <v>5347.949784392064</v>
+        <v>908.1424162175203</v>
       </c>
       <c r="I86" t="n">
-        <v>0.3300388405155058</v>
+        <v>0.1541539440267897</v>
       </c>
       <c r="J86" t="n">
-        <v>0.009661468838284126</v>
+        <v>0.002702192065707591</v>
       </c>
       <c r="K86" t="n">
-        <v>0.000803078033057851</v>
+        <v>0.0002117046666666666</v>
       </c>
     </row>
     <row r="87">
@@ -3637,34 +3637,34 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6412757396456613</v>
+        <v>0.06474221524857156</v>
       </c>
       <c r="C87" t="n">
-        <v>0.3207555662371512</v>
+        <v>0.0283745308594403</v>
       </c>
       <c r="D87" t="n">
-        <v>0.4539643589702126</v>
+        <v>0.1346760931611631</v>
       </c>
       <c r="E87" t="n">
-        <v>1.042711704924611</v>
+        <v>0.2072860618223624</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7597589142604019</v>
+        <v>0.2970588908009139</v>
       </c>
       <c r="G87" t="n">
-        <v>1.363447612685789</v>
+        <v>0.2891607017508115</v>
       </c>
       <c r="H87" t="n">
-        <v>22184.08284569364</v>
+        <v>3767.108407759297</v>
       </c>
       <c r="I87" t="n">
-        <v>1.142195196018426</v>
+        <v>0.5334944639839152</v>
       </c>
       <c r="J87" t="n">
-        <v>0.01927474749387337</v>
+        <v>0.005390905939692707</v>
       </c>
       <c r="K87" t="n">
-        <v>0.003837511198347108</v>
+        <v>0.001011631492374728</v>
       </c>
     </row>
     <row r="88">
@@ -3674,34 +3674,34 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.03402183736257047</v>
+        <v>0.003434792526061428</v>
       </c>
       <c r="C88" t="n">
-        <v>0.03980929672228795</v>
+        <v>0.003521591633125472</v>
       </c>
       <c r="D88" t="n">
-        <v>2.7402888836963</v>
+        <v>0.8129523688299022</v>
       </c>
       <c r="E88" t="n">
-        <v>1.708742469141675</v>
+        <v>0.3396897679618992</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4083325985721696</v>
+        <v>0.1596543673696591</v>
       </c>
       <c r="G88" t="n">
-        <v>0.5470164698810887</v>
+        <v>0.1160115466324993</v>
       </c>
       <c r="H88" t="n">
-        <v>14131.13962998717</v>
+        <v>2399.627484337444</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1802290479408939</v>
+        <v>0.08418105737156981</v>
       </c>
       <c r="J88" t="n">
-        <v>0.7877751692654615</v>
+        <v>0.2203308676539338</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0003101298512396702</v>
+        <v>8.175536383442288e-05</v>
       </c>
     </row>
     <row r="89">
@@ -3711,34 +3711,34 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8298188931883708</v>
+        <v>0.08377724289058312</v>
       </c>
       <c r="C89" t="n">
-        <v>0.6146801539620024</v>
+        <v>0.05437555208125405</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2721439346474938</v>
+        <v>0.08073603394542314</v>
       </c>
       <c r="E89" t="n">
-        <v>0.967896096945168</v>
+        <v>0.192413079513196</v>
       </c>
       <c r="F89" t="n">
-        <v>0.9427895189599589</v>
+        <v>0.368622208314074</v>
       </c>
       <c r="G89" t="n">
-        <v>1.663980135587908</v>
+        <v>0.3528978005676369</v>
       </c>
       <c r="H89" t="n">
-        <v>24888.29722880014</v>
+        <v>4226.314623758514</v>
       </c>
       <c r="I89" t="n">
-        <v>1.022371537340086</v>
+        <v>0.4775274464530856</v>
       </c>
       <c r="J89" t="n">
-        <v>0.05379859204954539</v>
+        <v>0.01504679371385723</v>
       </c>
       <c r="K89" t="n">
-        <v>0.004740896082644629</v>
+        <v>0.001249778705882353</v>
       </c>
     </row>
     <row r="90">
@@ -3748,34 +3748,34 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.164909316049295</v>
+        <v>0.1176074581059352</v>
       </c>
       <c r="C90" t="n">
-        <v>0.3498359444758395</v>
+        <v>0.03094702585747811</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1712707793452397</v>
+        <v>0.05081033120575443</v>
       </c>
       <c r="E90" t="n">
-        <v>1.148021262950676</v>
+        <v>0.2282210944420018</v>
       </c>
       <c r="F90" t="n">
-        <v>1.116240809261901</v>
+        <v>0.4364401001978965</v>
       </c>
       <c r="G90" t="n">
-        <v>2.090863026070251</v>
+        <v>0.4434313531799995</v>
       </c>
       <c r="H90" t="n">
-        <v>38240.37422386296</v>
+        <v>6493.648453108804</v>
       </c>
       <c r="I90" t="n">
-        <v>1.161130244489016</v>
+        <v>0.5423386121378737</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03975044402530283</v>
+        <v>0.01111770231332688</v>
       </c>
       <c r="K90" t="n">
-        <v>0.005314329037190082</v>
+        <v>0.00140094512745098</v>
       </c>
     </row>
     <row r="91">
@@ -3785,34 +3785,34 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1544831426539013</v>
+        <v>0.01559638117528205</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2011233041299447</v>
+        <v>0.0177916769038028</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1990001878684528</v>
+        <v>0.05903672240097434</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2707996328719762</v>
+        <v>0.05383366195647719</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2512958315538092</v>
+        <v>0.09825440621112902</v>
       </c>
       <c r="G91" t="n">
-        <v>0.3062552275160619</v>
+        <v>0.06495077308394333</v>
       </c>
       <c r="H91" t="n">
-        <v>3637.106084071149</v>
+        <v>617.6217878611385</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2916284344306646</v>
+        <v>0.1362132811023886</v>
       </c>
       <c r="J91" t="n">
-        <v>0.004544249639331523</v>
+        <v>0.001270969821000535</v>
       </c>
       <c r="K91" t="n">
-        <v>0.002376336264462809</v>
+        <v>0.0006264415860566446</v>
       </c>
     </row>
     <row r="92">
@@ -3822,34 +3822,34 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.677529522985912</v>
+        <v>0.06840234161774703</v>
       </c>
       <c r="C92" t="n">
-        <v>0.5950165921918041</v>
+        <v>0.05263608315542883</v>
       </c>
       <c r="D92" t="n">
-        <v>0.274125710826482</v>
+        <v>0.08132396087852301</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5355948922477274</v>
+        <v>0.1064736833986446</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3685895638463417</v>
+        <v>0.1441151988372183</v>
       </c>
       <c r="G92" t="n">
-        <v>0.6421698310847512</v>
+        <v>0.1361917225656251</v>
       </c>
       <c r="H92" t="n">
-        <v>8906.748898843351</v>
+        <v>1512.46679414321</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3842648797176189</v>
+        <v>0.1794817442302458</v>
       </c>
       <c r="J92" t="n">
-        <v>0.01875639164632462</v>
+        <v>0.005245928288581416</v>
       </c>
       <c r="K92" t="n">
-        <v>0.002053405123966943</v>
+        <v>0.0005413115904139436</v>
       </c>
     </row>
     <row r="93">
@@ -3859,34 +3859,34 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8022723837632084</v>
+        <v>0.08099618954286705</v>
       </c>
       <c r="C93" t="n">
-        <v>1.917241827955508</v>
+        <v>0.1696021617037565</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4478015267270115</v>
+        <v>0.1328477862623467</v>
       </c>
       <c r="E93" t="n">
-        <v>2.56317436782474</v>
+        <v>0.5095467116760024</v>
       </c>
       <c r="F93" t="n">
-        <v>1.436268627995125</v>
+        <v>0.5615680941890849</v>
       </c>
       <c r="G93" t="n">
-        <v>1.620098359668862</v>
+        <v>0.3435913299700404</v>
       </c>
       <c r="H93" t="n">
-        <v>3694.144298015863</v>
+        <v>627.3075223045804</v>
       </c>
       <c r="I93" t="n">
-        <v>1.791009156421505</v>
+        <v>0.8365413138018143</v>
       </c>
       <c r="J93" t="n">
-        <v>0.03787067380307001</v>
+        <v>0.01059195407929614</v>
       </c>
       <c r="K93" t="n">
-        <v>0.003986788578512397</v>
+        <v>0.001050983481481482</v>
       </c>
     </row>
     <row r="94">
@@ -3896,34 +3896,34 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.86726039392369</v>
+        <v>0.1885157458402192</v>
       </c>
       <c r="C94" t="n">
-        <v>5.681811515300675</v>
+        <v>0.5026217878919828</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3002443015469413</v>
+        <v>0.08907247612559258</v>
       </c>
       <c r="E94" t="n">
-        <v>1.161579668848862</v>
+        <v>0.230916440192846</v>
       </c>
       <c r="F94" t="n">
-        <v>0.826583562170635</v>
+        <v>0.32318672610996</v>
       </c>
       <c r="G94" t="n">
-        <v>1.394450561113318</v>
+        <v>0.2957358236992004</v>
       </c>
       <c r="H94" t="n">
-        <v>4403.983541120691</v>
+        <v>747.8462616997399</v>
       </c>
       <c r="I94" t="n">
-        <v>1.546021721283841</v>
+        <v>0.7221130261963621</v>
       </c>
       <c r="J94" t="n">
-        <v>0.02999922390182321</v>
+        <v>0.008390407935041179</v>
       </c>
       <c r="K94" t="n">
-        <v>0.004366646090909091</v>
+        <v>0.001151120211328976</v>
       </c>
     </row>
     <row r="95">
@@ -3933,34 +3933,34 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.53211680596508</v>
+        <v>0.2556386296118099</v>
       </c>
       <c r="C95" t="n">
-        <v>1.717320425857351</v>
+        <v>0.1519168069027657</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2244557728215301</v>
+        <v>0.06658854593705391</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9093544398425358</v>
+        <v>0.1807752802096607</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5386357869282302</v>
+        <v>0.210601740114281</v>
       </c>
       <c r="G95" t="n">
-        <v>0.9359200287979544</v>
+        <v>0.1984904222148682</v>
       </c>
       <c r="H95" t="n">
-        <v>9868.791675795745</v>
+        <v>1675.832548720032</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6353635419897741</v>
+        <v>0.2967644527400796</v>
       </c>
       <c r="J95" t="n">
-        <v>0.01135656930268963</v>
+        <v>0.003176290476846005</v>
       </c>
       <c r="K95" t="n">
-        <v>0.001329796294765841</v>
+        <v>0.0003505563217138711</v>
       </c>
     </row>
     <row r="96">
@@ -3970,34 +3970,34 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1.125202805215951</v>
+        <v>0.1135987496639746</v>
       </c>
       <c r="C96" t="n">
-        <v>2.159729283592199</v>
+        <v>0.1910529750870022</v>
       </c>
       <c r="D96" t="n">
-        <v>0.5989454741840772</v>
+        <v>0.1776871573412762</v>
       </c>
       <c r="E96" t="n">
-        <v>1.175118054838088</v>
+        <v>0.2336078060822705</v>
       </c>
       <c r="F96" t="n">
-        <v>0.6213242134062867</v>
+        <v>0.242932169926422</v>
       </c>
       <c r="G96" t="n">
-        <v>0.7410440300953655</v>
+        <v>0.1571610157786144</v>
       </c>
       <c r="H96" t="n">
-        <v>2825.262183111137</v>
+        <v>479.7615027924572</v>
       </c>
       <c r="I96" t="n">
-        <v>1.009705501917041</v>
+        <v>0.4716114175620749</v>
       </c>
       <c r="J96" t="n">
-        <v>0.03024794328429511</v>
+        <v>0.008459971637326289</v>
       </c>
       <c r="K96" t="n">
-        <v>0.002891854561983471</v>
+        <v>0.0007623407450980393</v>
       </c>
     </row>
     <row r="97">
@@ -4007,34 +4007,34 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1.448768466652879</v>
+        <v>0.1462654426397156</v>
       </c>
       <c r="C97" t="n">
-        <v>3.045853418720604</v>
+        <v>0.2694408793483611</v>
       </c>
       <c r="D97" t="n">
-        <v>0.732705084517297</v>
+        <v>0.2173691750734648</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8830427149818332</v>
+        <v>0.1755446361108463</v>
       </c>
       <c r="F97" t="n">
-        <v>0.4634688928910917</v>
+        <v>0.1812121617249854</v>
       </c>
       <c r="G97" t="n">
-        <v>0.7281881524294167</v>
+        <v>0.1544345343407354</v>
       </c>
       <c r="H97" t="n">
-        <v>3805.529586468883</v>
+        <v>646.222005249433</v>
       </c>
       <c r="I97" t="n">
-        <v>1.138249178370524</v>
+        <v>0.5316513652059854</v>
       </c>
       <c r="J97" t="n">
-        <v>0.02910223953783151</v>
+        <v>0.008139532620737249</v>
       </c>
       <c r="K97" t="n">
-        <v>0.002196930008264462</v>
+        <v>0.0005791471263616556</v>
       </c>
     </row>
     <row r="98">
@@ -4044,34 +4044,34 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.68573726066946</v>
+        <v>0.1701894486810062</v>
       </c>
       <c r="C98" t="n">
-        <v>3.582596795775843</v>
+        <v>0.3169220242417092</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5776268970897946</v>
+        <v>0.1713626461366391</v>
       </c>
       <c r="E98" t="n">
-        <v>0.755611295817905</v>
+        <v>0.1502118841083787</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4091983019415019</v>
+        <v>0.1599928495879386</v>
       </c>
       <c r="G98" t="n">
-        <v>0.7093653205966297</v>
+        <v>0.1504425780594195</v>
       </c>
       <c r="H98" t="n">
-        <v>3723.046180261896</v>
+        <v>632.2153891010767</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9185182191132701</v>
+        <v>0.4290198266228648</v>
       </c>
       <c r="J98" t="n">
-        <v>0.01837306760102471</v>
+        <v>0.005138717344661597</v>
       </c>
       <c r="K98" t="n">
-        <v>0.001642445661157025</v>
+        <v>0.000432975871459695</v>
       </c>
     </row>
     <row r="99">
@@ -4081,34 +4081,34 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5.322705972579626</v>
+        <v>0.5373722323754511</v>
       </c>
       <c r="C99" t="n">
-        <v>6.306384035522563</v>
+        <v>0.5578724339116113</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2395776998198699</v>
+        <v>0.07107471761322806</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2874006886939594</v>
+        <v>0.05713387184879915</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2918991362283426</v>
+        <v>0.114129932543334</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4565059265143228</v>
+        <v>0.09681602199901074</v>
       </c>
       <c r="H99" t="n">
-        <v>8742.643924305012</v>
+        <v>1484.599911674436</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1607492394995086</v>
+        <v>0.07508246371684868</v>
       </c>
       <c r="J99" t="n">
-        <v>1.256983240223636e-05</v>
+        <v>3.515625000000481e-06</v>
       </c>
       <c r="K99" t="n">
-        <v>0.0001159394049586769</v>
+        <v>3.056354684095841e-05</v>
       </c>
     </row>
     <row r="100">
@@ -4118,34 +4118,34 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.3766438278636142</v>
+        <v>0.0380253832603521</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2022919277037299</v>
+        <v>0.01789505514302226</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2301730811679978</v>
+        <v>0.068284680746506</v>
       </c>
       <c r="E100" t="n">
-        <v>0.6297523386504428</v>
+        <v>0.1251917299726784</v>
       </c>
       <c r="F100" t="n">
-        <v>0.4242257253321998</v>
+        <v>0.1658684367515087</v>
       </c>
       <c r="G100" t="n">
-        <v>0.6659445564108006</v>
+        <v>0.1412338790777269</v>
       </c>
       <c r="H100" t="n">
-        <v>13585.49539137277</v>
+        <v>2306.970915516131</v>
       </c>
       <c r="I100" t="n">
-        <v>0.5522741234521837</v>
+        <v>0.2579551975795179</v>
       </c>
       <c r="J100" t="n">
-        <v>0.002908409056355481</v>
+        <v>0.0008134456579494234</v>
       </c>
       <c r="K100" t="n">
-        <v>0.002723543966942149</v>
+        <v>0.0007179712854030502</v>
       </c>
     </row>
     <row r="101">
@@ -4155,34 +4155,34 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.1082975183881285</v>
+        <v>0.01093355137720402</v>
       </c>
       <c r="C101" t="n">
-        <v>0.04351687912563054</v>
+        <v>0.003849570076498086</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3350711026800591</v>
+        <v>0.09940442712841752</v>
       </c>
       <c r="E101" t="n">
-        <v>0.1696392397977299</v>
+        <v>0.03372346333328365</v>
       </c>
       <c r="F101" t="n">
-        <v>0.121116905397914</v>
+        <v>0.0473556188672925</v>
       </c>
       <c r="G101" t="n">
-        <v>0.246581492956331</v>
+        <v>0.05229513541892657</v>
       </c>
       <c r="H101" t="n">
-        <v>1810.815871720211</v>
+        <v>307.4970348204131</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1518755887474277</v>
+        <v>0.07093777499108249</v>
       </c>
       <c r="J101" t="n">
-        <v>0.00542774443515492</v>
+        <v>0.001518072271707391</v>
       </c>
       <c r="K101" t="n">
-        <v>0.0002429618264462812</v>
+        <v>6.404876034858395e-05</v>
       </c>
     </row>
     <row r="102">
@@ -4192,34 +4192,34 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7200918988925394</v>
+        <v>0.07269937381790495</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2601495183536836</v>
+        <v>0.02301322662359509</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3238281169885795</v>
+        <v>0.09606900803994525</v>
       </c>
       <c r="E102" t="n">
-        <v>1.189689913921319</v>
+        <v>0.2365046214421899</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8812062534862138</v>
+        <v>0.3445437063180332</v>
       </c>
       <c r="G102" t="n">
-        <v>1.501175786119491</v>
+        <v>0.3183701667206438</v>
       </c>
       <c r="H102" t="n">
-        <v>31791.94083674169</v>
+        <v>5398.631462842928</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9581356551109085</v>
+        <v>0.4475242668933667</v>
       </c>
       <c r="J102" t="n">
-        <v>0.03245882778388905</v>
+        <v>0.009078328395806469</v>
       </c>
       <c r="K102" t="n">
-        <v>0.004255687760330579</v>
+        <v>0.001121869758169935</v>
       </c>
     </row>
     <row r="103">
@@ -4229,34 +4229,34 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7265910988784851</v>
+        <v>0.07335552308166175</v>
       </c>
       <c r="C103" t="n">
-        <v>0.2646285811395462</v>
+        <v>0.02340945140849831</v>
       </c>
       <c r="D103" t="n">
-        <v>0.5813223282475186</v>
+        <v>0.1724589573800972</v>
       </c>
       <c r="E103" t="n">
-        <v>1.175633154609666</v>
+        <v>0.2337102054344516</v>
       </c>
       <c r="F103" t="n">
-        <v>0.8502352845470929</v>
+        <v>0.332434336480575</v>
       </c>
       <c r="G103" t="n">
-        <v>1.573965774295163</v>
+        <v>0.3338075064948131</v>
       </c>
       <c r="H103" t="n">
-        <v>31420.17148836304</v>
+        <v>5335.500818778629</v>
       </c>
       <c r="I103" t="n">
-        <v>1.008599480220583</v>
+        <v>0.471094818950766</v>
       </c>
       <c r="J103" t="n">
-        <v>0.04416466913622191</v>
+        <v>0.01235230589903706</v>
       </c>
       <c r="K103" t="n">
-        <v>0.004396506421487603</v>
+        <v>0.001158991888888889</v>
       </c>
     </row>
     <row r="104">
@@ -4266,34 +4266,34 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.130501252089724</v>
+        <v>0.01317520628126287</v>
       </c>
       <c r="C104" t="n">
-        <v>0.06458188627157468</v>
+        <v>0.005713013016331606</v>
       </c>
       <c r="D104" t="n">
-        <v>0.05776565178776168</v>
+        <v>0.01713714336370263</v>
       </c>
       <c r="E104" t="n">
-        <v>0.1957636524980206</v>
+        <v>0.03891687067731735</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2313092228757696</v>
+        <v>0.09043982227755315</v>
       </c>
       <c r="G104" t="n">
-        <v>0.4406207282800522</v>
+        <v>0.09344708062852114</v>
       </c>
       <c r="H104" t="n">
-        <v>4409.926591853819</v>
+        <v>748.8554589940447</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2811036158547825</v>
+        <v>0.1312973678992503</v>
       </c>
       <c r="J104" t="n">
-        <v>0.03597123739088302</v>
+        <v>0.01006070545776259</v>
       </c>
       <c r="K104" t="n">
-        <v>0.0004983175123966936</v>
+        <v>0.0001313647472766883</v>
       </c>
     </row>
     <row r="105">
@@ -4303,34 +4303,34 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.90282130622434</v>
+        <v>0.1921059210117864</v>
       </c>
       <c r="C105" t="n">
-        <v>2.398932993445813</v>
+        <v>0.2122133032663604</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2114625667147722</v>
+        <v>0.06273389479204909</v>
       </c>
       <c r="E105" t="n">
-        <v>2.005936376986117</v>
+        <v>0.3987704845815775</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9223597846080073</v>
+        <v>0.3606343662341218</v>
       </c>
       <c r="G105" t="n">
-        <v>1.508417237096082</v>
+        <v>0.3199059375317866</v>
       </c>
       <c r="H105" t="n">
-        <v>10381.60968880259</v>
+        <v>1762.914852815534</v>
       </c>
       <c r="I105" t="n">
-        <v>1.292220140672445</v>
+        <v>0.6035678434828088</v>
       </c>
       <c r="J105" t="n">
-        <v>0.0316711313613954</v>
+        <v>0.008858019552640274</v>
       </c>
       <c r="K105" t="n">
-        <v>0.004006072132231406</v>
+        <v>0.001056066945533769</v>
       </c>
     </row>
     <row r="106">
@@ -4340,34 +4340,34 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8124764410199488</v>
+        <v>0.08202637551511303</v>
       </c>
       <c r="C106" t="n">
-        <v>1.227051611867544</v>
+        <v>0.1085468733575135</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3308743885627989</v>
+        <v>0.098159401940297</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7451109968396079</v>
+        <v>0.1481244752753437</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4272266429426237</v>
+        <v>0.1670417685018907</v>
       </c>
       <c r="G106" t="n">
-        <v>0.8703469894869623</v>
+        <v>0.184583656830792</v>
       </c>
       <c r="H106" t="n">
-        <v>9633.534496671156</v>
+        <v>1635.883216415857</v>
       </c>
       <c r="I106" t="n">
-        <v>0.6330386430534221</v>
+        <v>0.2956785431545819</v>
       </c>
       <c r="J106" t="n">
-        <v>0.01617942387360016</v>
+        <v>0.004525182614647544</v>
       </c>
       <c r="K106" t="n">
-        <v>0.002286326338842976</v>
+        <v>0.0006027134793028324</v>
       </c>
     </row>
     <row r="107">
@@ -4377,34 +4377,34 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.55161145253848</v>
+        <v>0.05568984632656859</v>
       </c>
       <c r="C107" t="n">
-        <v>0.4385334127237631</v>
+        <v>0.03879334035633289</v>
       </c>
       <c r="D107" t="n">
-        <v>3.102168498187701</v>
+        <v>0.9203099877956846</v>
       </c>
       <c r="E107" t="n">
-        <v>1.691286357296049</v>
+        <v>0.3362195770528289</v>
       </c>
       <c r="F107" t="n">
-        <v>0.3632103230454375</v>
+        <v>0.1420119641456936</v>
       </c>
       <c r="G107" t="n">
-        <v>0.705387310635137</v>
+        <v>0.1495989195709418</v>
       </c>
       <c r="H107" t="n">
-        <v>9093.263616994644</v>
+        <v>1544.139104772675</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4075540329232957</v>
+        <v>0.1903595997398932</v>
       </c>
       <c r="J107" t="n">
-        <v>0.7487458095785881</v>
+        <v>0.2094148436165113</v>
       </c>
       <c r="K107" t="n">
-        <v>0.00104754196694215</v>
+        <v>0.0002761494074074076</v>
       </c>
     </row>
     <row r="108">
@@ -4414,34 +4414,34 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.220365452099666</v>
+        <v>0.02224775810335286</v>
       </c>
       <c r="C108" t="n">
-        <v>0.2042646000681234</v>
+        <v>0.01806956077525707</v>
       </c>
       <c r="D108" t="n">
-        <v>2.503554589906714</v>
+        <v>0.7427211950056583</v>
       </c>
       <c r="E108" t="n">
-        <v>1.408003993134799</v>
+        <v>0.2799044082737853</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3779415510928316</v>
+        <v>0.1477717415984585</v>
       </c>
       <c r="G108" t="n">
-        <v>0.5006373795892836</v>
+        <v>0.1061754442618883</v>
       </c>
       <c r="H108" t="n">
-        <v>4274.648761671254</v>
+        <v>725.883751981911</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2058406406249567</v>
+        <v>0.09614367370754152</v>
       </c>
       <c r="J108" t="n">
-        <v>0.5942650203930208</v>
+        <v>0.166208497891173</v>
       </c>
       <c r="K108" t="n">
-        <v>0.0008710299256198356</v>
+        <v>0.0002296179106753815</v>
       </c>
     </row>
     <row r="109">
@@ -4451,34 +4451,34 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7565198442682844</v>
+        <v>0.07637708331909837</v>
       </c>
       <c r="C109" t="n">
-        <v>0.3085455761723072</v>
+        <v>0.0272944163537041</v>
       </c>
       <c r="D109" t="n">
-        <v>0.1486125617916733</v>
+        <v>0.04408839333152973</v>
       </c>
       <c r="E109" t="n">
-        <v>0.7662151397321743</v>
+        <v>0.1523198771756732</v>
       </c>
       <c r="F109" t="n">
-        <v>0.7750292966225673</v>
+        <v>0.3030294727335083</v>
       </c>
       <c r="G109" t="n">
-        <v>1.606932870363923</v>
+        <v>0.34079918592953</v>
       </c>
       <c r="H109" t="n">
-        <v>26936.63373450616</v>
+        <v>4574.145351142555</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8293504409962797</v>
+        <v>0.3873715022760401</v>
       </c>
       <c r="J109" t="n">
-        <v>0.01491937872356452</v>
+        <v>0.004172763736746951</v>
       </c>
       <c r="K109" t="n">
-        <v>0.004486776404958678</v>
+        <v>0.001182788551198257</v>
       </c>
     </row>
     <row r="110">
@@ -4488,34 +4488,34 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.730633450336306</v>
+        <v>0.07376363268571012</v>
       </c>
       <c r="C110" t="n">
-        <v>0.2909563313339901</v>
+        <v>0.02573844469492989</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4571642996579245</v>
+        <v>0.1356254088985176</v>
       </c>
       <c r="E110" t="n">
-        <v>1.070057417790296</v>
+        <v>0.2127222577534925</v>
       </c>
       <c r="F110" t="n">
-        <v>0.6402142470104184</v>
+        <v>0.2503180028851546</v>
       </c>
       <c r="G110" t="n">
-        <v>1.304859937525521</v>
+        <v>0.2767353961463521</v>
       </c>
       <c r="H110" t="n">
-        <v>20030.46498998165</v>
+        <v>3401.399715279902</v>
       </c>
       <c r="I110" t="n">
-        <v>0.926330483028037</v>
+        <v>0.4326687647065111</v>
       </c>
       <c r="J110" t="n">
-        <v>0.04869539076470048</v>
+        <v>0.01361949210450216</v>
       </c>
       <c r="K110" t="n">
-        <v>0.00493403926446281</v>
+        <v>0.001300694446623094</v>
       </c>
     </row>
     <row r="111">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.1109892995663487</v>
+        <v>0.01120530947698601</v>
       </c>
       <c r="C111" t="n">
-        <v>0.08994359314258907</v>
+        <v>0.007956548624152109</v>
       </c>
       <c r="D111" t="n">
-        <v>1.503807461683818</v>
+        <v>0.4461295469661994</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5916680950966331</v>
+        <v>0.1176207658927042</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1235589563567793</v>
+        <v>0.04831043879174975</v>
       </c>
       <c r="G111" t="n">
-        <v>0.2055224739132605</v>
+        <v>0.04358731661516128</v>
       </c>
       <c r="H111" t="n">
-        <v>1696.720660587378</v>
+        <v>288.1223763261585</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2120143018659923</v>
+        <v>0.09902725622135855</v>
       </c>
       <c r="J111" t="n">
-        <v>0.385212565632817</v>
+        <v>0.1077391394504285</v>
       </c>
       <c r="K111" t="n">
-        <v>0.0003538774049586769</v>
+        <v>9.328794335511962e-05</v>
       </c>
     </row>
     <row r="112">
@@ -4562,34 +4562,34 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.3612043864729291</v>
+        <v>0.03646664093464715</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3576053756858691</v>
+        <v>0.03163432169528842</v>
       </c>
       <c r="D112" t="n">
-        <v>0.07410125653063809</v>
+        <v>0.02198337277075596</v>
       </c>
       <c r="E112" t="n">
-        <v>0.3411040988349749</v>
+        <v>0.06780985097321789</v>
       </c>
       <c r="F112" t="n">
-        <v>0.3102951716569807</v>
+        <v>0.1213226166658825</v>
       </c>
       <c r="G112" t="n">
-        <v>0.4236917448883187</v>
+        <v>0.08985677274141524</v>
       </c>
       <c r="H112" t="n">
-        <v>5157.371080322892</v>
+        <v>875.7799947718119</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2089148507613318</v>
+        <v>0.09757957021156854</v>
       </c>
       <c r="J112" t="n">
-        <v>0.01885351563872007</v>
+        <v>0.005273092655204519</v>
       </c>
       <c r="K112" t="n">
-        <v>0.0008109990165289247</v>
+        <v>0.0002137927690631806</v>
       </c>
     </row>
     <row r="113">
@@ -4599,34 +4599,34 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.3195393652183348</v>
+        <v>0.03226020428402358</v>
       </c>
       <c r="C113" t="n">
-        <v>0.3868227598837975</v>
+        <v>0.03421893645125901</v>
       </c>
       <c r="D113" t="n">
-        <v>2.261885896634851</v>
+        <v>0.6710261493350057</v>
       </c>
       <c r="E113" t="n">
-        <v>1.381120039064679</v>
+        <v>0.2745600077658699</v>
       </c>
       <c r="F113" t="n">
-        <v>0.317391319765523</v>
+        <v>0.1240971466470604</v>
       </c>
       <c r="G113" t="n">
-        <v>0.32805606322268</v>
+        <v>0.0695743060257496</v>
       </c>
       <c r="H113" t="n">
-        <v>2501.93275852333</v>
+        <v>424.8565061643391</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3136045171718829</v>
+        <v>0.1464778300370729</v>
       </c>
       <c r="J113" t="n">
-        <v>0.6114630043812126</v>
+        <v>0.1710185590378704</v>
       </c>
       <c r="K113" t="n">
-        <v>0.000389230851239669</v>
+        <v>0.0001026076971677559</v>
       </c>
     </row>
     <row r="114">
@@ -4636,34 +4636,34 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>15.29752822599251</v>
+        <v>1.544414990227998</v>
       </c>
       <c r="C114" t="n">
-        <v>19.92605876835092</v>
+        <v>1.762689814123351</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3833491835410994</v>
+        <v>0.1137269244505262</v>
       </c>
       <c r="E114" t="n">
-        <v>1.174300406132146</v>
+        <v>0.233445261460005</v>
       </c>
       <c r="F114" t="n">
-        <v>0.6128620622004429</v>
+        <v>0.2396235450405335</v>
       </c>
       <c r="G114" t="n">
-        <v>0.9033495221009507</v>
+        <v>0.1915828516670472</v>
       </c>
       <c r="H114" t="n">
-        <v>5795.939995152128</v>
+        <v>984.2162255918707</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7814691970115102</v>
+        <v>0.3650072175341827</v>
       </c>
       <c r="J114" t="n">
-        <v>0.03598178204158198</v>
+        <v>0.01006365466475496</v>
       </c>
       <c r="K114" t="n">
-        <v>0.002147740280991736</v>
+        <v>0.0005661798997821352</v>
       </c>
     </row>
     <row r="115">
@@ -4673,34 +4673,34 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4419327523627424</v>
+        <v>0.0446168529541938</v>
       </c>
       <c r="C115" t="n">
-        <v>0.6571083792406376</v>
+        <v>0.05812881816359486</v>
       </c>
       <c r="D115" t="n">
-        <v>2.636219699409772</v>
+        <v>0.7820785108248988</v>
       </c>
       <c r="E115" t="n">
-        <v>1.889310178486562</v>
+        <v>0.3755857583738345</v>
       </c>
       <c r="F115" t="n">
-        <v>0.475593435013374</v>
+        <v>0.1859527484646886</v>
       </c>
       <c r="G115" t="n">
-        <v>0.5760451639107208</v>
+        <v>0.1221679676481797</v>
       </c>
       <c r="H115" t="n">
-        <v>3109.707891157667</v>
+        <v>528.0636041588491</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4970842836110035</v>
+        <v>0.2321772271187197</v>
       </c>
       <c r="J115" t="n">
-        <v>0.6796992579789504</v>
+        <v>0.1901033862159877</v>
       </c>
       <c r="K115" t="n">
-        <v>0.003014446173553718</v>
+        <v>0.0007946579237472764</v>
       </c>
     </row>
     <row r="116">
@@ -4710,34 +4710,34 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.323447108843681</v>
+        <v>0.03265472408773265</v>
       </c>
       <c r="C116" t="n">
-        <v>0.337486220287857</v>
+        <v>0.0298545502562335</v>
       </c>
       <c r="D116" t="n">
-        <v>1.824586902748519</v>
+        <v>0.5412941144820607</v>
       </c>
       <c r="E116" t="n">
-        <v>1.435003412434173</v>
+        <v>0.2852717627128175</v>
       </c>
       <c r="F116" t="n">
-        <v>0.310673381553806</v>
+        <v>0.1214704933282449</v>
       </c>
       <c r="G116" t="n">
-        <v>0.4000156196576475</v>
+        <v>0.08483552739048095</v>
       </c>
       <c r="H116" t="n">
-        <v>1976.933203029183</v>
+        <v>335.7056382502386</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3687592142928536</v>
+        <v>0.1722393860997485</v>
       </c>
       <c r="J116" t="n">
-        <v>0.4410204939093118</v>
+        <v>0.1233479193902606</v>
       </c>
       <c r="K116" t="n">
-        <v>0.002047242545454546</v>
+        <v>0.0005396870326797385</v>
       </c>
     </row>
     <row r="117">
@@ -4747,34 +4747,34 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1.72213942270417</v>
+        <v>0.1738645551356287</v>
       </c>
       <c r="C117" t="n">
-        <v>2.778944588456525</v>
+        <v>0.2458297135942311</v>
       </c>
       <c r="D117" t="n">
-        <v>0.2033895850000216</v>
+        <v>0.06033891021667306</v>
       </c>
       <c r="E117" t="n">
-        <v>4.873325408879492</v>
+        <v>0.9687936053796581</v>
       </c>
       <c r="F117" t="n">
-        <v>1.806472210681689</v>
+        <v>0.7063143598521198</v>
       </c>
       <c r="G117" t="n">
-        <v>2.310625000724512</v>
+        <v>0.4900385907576817</v>
       </c>
       <c r="H117" t="n">
-        <v>5114.949390234098</v>
+        <v>868.5763115491865</v>
       </c>
       <c r="I117" t="n">
-        <v>2.394189015121539</v>
+        <v>1.118273470025904</v>
       </c>
       <c r="J117" t="n">
-        <v>0.08479753824865768</v>
+        <v>0.02371681147892145</v>
       </c>
       <c r="K117" t="n">
-        <v>0.01288992679338843</v>
+        <v>0.003397998130718954</v>
       </c>
     </row>
     <row r="118">
@@ -4784,34 +4784,34 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7693053634068788</v>
+        <v>0.07766788972414496</v>
       </c>
       <c r="C118" t="n">
-        <v>1.738568133975308</v>
+        <v>0.1537964118516618</v>
       </c>
       <c r="D118" t="n">
-        <v>0.02312074772333275</v>
+        <v>0.006859155157922048</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9527858778315859</v>
+        <v>0.189409240773749</v>
       </c>
       <c r="F118" t="n">
-        <v>0.552151138263869</v>
+        <v>0.2158861207265938</v>
       </c>
       <c r="G118" t="n">
-        <v>0.6723020715695579</v>
+        <v>0.142582184306027</v>
       </c>
       <c r="H118" t="n">
-        <v>3364.590404847624</v>
+        <v>571.3455404458228</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5380954393069534</v>
+        <v>0.2513326434623012</v>
       </c>
       <c r="J118" t="n">
-        <v>4.469273743015028e-06</v>
+        <v>1.249999999999516e-06</v>
       </c>
       <c r="K118" t="n">
-        <v>0.001116721082644628</v>
+        <v>0.0002943861677559913</v>
       </c>
     </row>
     <row r="119">
@@ -4821,34 +4821,34 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.815883136878743</v>
+        <v>0.08237031030469098</v>
       </c>
       <c r="C119" t="n">
-        <v>1.34218870162707</v>
+        <v>0.1187320774516254</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3844422321728058</v>
+        <v>0.1140511955445991</v>
       </c>
       <c r="E119" t="n">
-        <v>4.282709287192668</v>
+        <v>0.8513819667310725</v>
       </c>
       <c r="F119" t="n">
-        <v>1.703438616358425</v>
+        <v>0.6660291527023032</v>
       </c>
       <c r="G119" t="n">
-        <v>2.308783853777571</v>
+        <v>0.4896481193246393</v>
       </c>
       <c r="H119" t="n">
-        <v>4954.364311702646</v>
+        <v>841.3071472702605</v>
       </c>
       <c r="I119" t="n">
-        <v>2.108664391011944</v>
+        <v>0.9849111455961136</v>
       </c>
       <c r="J119" t="n">
-        <v>0.07921459451255722</v>
+        <v>0.02215533190273085</v>
       </c>
       <c r="K119" t="n">
-        <v>0.01267652087603306</v>
+        <v>0.003341740797385621</v>
       </c>
     </row>
     <row r="120">
@@ -4858,34 +4858,34 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1.426445944548293</v>
+        <v>0.1440117950406584</v>
       </c>
       <c r="C120" t="n">
-        <v>2.588815416743499</v>
+        <v>0.2290105945580787</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2970946648985994</v>
+        <v>0.08813808391991781</v>
       </c>
       <c r="E120" t="n">
-        <v>1.327192631277051</v>
+        <v>0.2638394989888112</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6148837076133424</v>
+        <v>0.2404139901839555</v>
       </c>
       <c r="G120" t="n">
-        <v>1.221234515991753</v>
+        <v>0.2590000718479155</v>
       </c>
       <c r="H120" t="n">
-        <v>3354.729208195287</v>
+        <v>569.6709976180675</v>
       </c>
       <c r="I120" t="n">
-        <v>1.0182521641417</v>
+        <v>0.4756033770785305</v>
       </c>
       <c r="J120" t="n">
-        <v>0.02896716016416578</v>
+        <v>0.008101752608415117</v>
       </c>
       <c r="K120" t="n">
-        <v>0.004672537760330578</v>
+        <v>0.001231758320261438</v>
       </c>
     </row>
     <row r="121">
@@ -4895,34 +4895,34 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.335293785802761</v>
+        <v>0.1348092128797675</v>
       </c>
       <c r="C121" t="n">
-        <v>1.427841653652196</v>
+        <v>0.1263090693615404</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4839743211704932</v>
+        <v>0.143579048613913</v>
       </c>
       <c r="E121" t="n">
-        <v>1.267381831239637</v>
+        <v>0.2519494001861929</v>
       </c>
       <c r="F121" t="n">
-        <v>0.6028031295052233</v>
+        <v>0.2356905929777179</v>
       </c>
       <c r="G121" t="n">
-        <v>1.667397560861861</v>
+        <v>0.353622569954596</v>
       </c>
       <c r="H121" t="n">
-        <v>7928.402742160562</v>
+        <v>1346.332541121605</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7035525940886036</v>
+        <v>0.3286140717245123</v>
       </c>
       <c r="J121" t="n">
-        <v>0.02506619831032532</v>
+        <v>0.007010702339919111</v>
       </c>
       <c r="K121" t="n">
-        <v>0.002325614033057851</v>
+        <v>0.0006130703660130719</v>
       </c>
     </row>
     <row r="122">
@@ -4932,34 +4932,34 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.075474086830717</v>
+        <v>0.1085782145170948</v>
       </c>
       <c r="C122" t="n">
-        <v>2.581264196481925</v>
+        <v>0.228342601996478</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1754441513011926</v>
+        <v>0.05204843155268712</v>
       </c>
       <c r="E122" t="n">
-        <v>1.124641941265117</v>
+        <v>0.2235733979623425</v>
       </c>
       <c r="F122" t="n">
-        <v>0.7278917162913551</v>
+        <v>0.2845991034868902</v>
       </c>
       <c r="G122" t="n">
-        <v>1.168545431146278</v>
+        <v>0.2478257424444455</v>
       </c>
       <c r="H122" t="n">
-        <v>2550.321903807776</v>
+        <v>433.0735308352827</v>
       </c>
       <c r="I122" t="n">
-        <v>1.359181070712341</v>
+        <v>0.6348438334397146</v>
       </c>
       <c r="J122" t="n">
-        <v>0.02708019418411674</v>
+        <v>0.007573991810870151</v>
       </c>
       <c r="K122" t="n">
-        <v>0.00292175073553719</v>
+        <v>0.0007702218714596951</v>
       </c>
     </row>
     <row r="123">
@@ -4969,34 +4969,34 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2.650194638629332</v>
+        <v>0.2675595865197665</v>
       </c>
       <c r="C123" t="n">
-        <v>6.722247685240699</v>
+        <v>0.5946603721559079</v>
       </c>
       <c r="D123" t="n">
-        <v>0.392186410639304</v>
+        <v>0.1163486351563268</v>
       </c>
       <c r="E123" t="n">
-        <v>1.780863746496139</v>
+        <v>0.3540271303275457</v>
       </c>
       <c r="F123" t="n">
-        <v>0.8559638805415042</v>
+        <v>0.3346741659054169</v>
       </c>
       <c r="G123" t="n">
-        <v>1.192401168769062</v>
+        <v>0.2528850800879353</v>
       </c>
       <c r="H123" t="n">
-        <v>3422.217045959929</v>
+        <v>581.1311964837615</v>
       </c>
       <c r="I123" t="n">
-        <v>1.339413760442702</v>
+        <v>0.6256109539516324</v>
       </c>
       <c r="J123" t="n">
-        <v>0.04843491026773079</v>
+        <v>0.01354663896550595</v>
       </c>
       <c r="K123" t="n">
-        <v>0.006743563933884297</v>
+        <v>0.001777715111111111</v>
       </c>
     </row>
     <row r="124">
@@ -5006,34 +5006,34 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.776905694560423</v>
+        <v>0.179393673955621</v>
       </c>
       <c r="C124" t="n">
-        <v>2.693395656622097</v>
+        <v>0.2382619234704163</v>
       </c>
       <c r="D124" t="n">
-        <v>2.183745331264515</v>
+        <v>0.6478444482751393</v>
       </c>
       <c r="E124" t="n">
-        <v>1.598223151598985</v>
+        <v>0.3177190602576295</v>
       </c>
       <c r="F124" t="n">
-        <v>0.4400594888296924</v>
+        <v>0.1720592956325104</v>
       </c>
       <c r="G124" t="n">
-        <v>0.4083264741275481</v>
+        <v>0.08659809786866121</v>
       </c>
       <c r="H124" t="n">
-        <v>2955.626635367138</v>
+        <v>501.8988626095139</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5282274926600833</v>
+        <v>0.2467235408103681</v>
       </c>
       <c r="J124" t="n">
-        <v>0.6413178200493582</v>
+        <v>0.1793685777950549</v>
       </c>
       <c r="K124" t="n">
-        <v>0.001780607809917355</v>
+        <v>0.0004693977015250543</v>
       </c>
     </row>
     <row r="125">
@@ -5043,34 +5043,34 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2.638536839885771</v>
+        <v>0.266382633036391</v>
       </c>
       <c r="C125" t="n">
-        <v>6.976236873584845</v>
+        <v>0.6171286465094286</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1978197181148857</v>
+        <v>0.05868651637408275</v>
       </c>
       <c r="E125" t="n">
-        <v>1.719379259049869</v>
+        <v>0.34180431053401</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7688642261419104</v>
+        <v>0.3006189857167469</v>
       </c>
       <c r="G125" t="n">
-        <v>1.158594084364702</v>
+        <v>0.245715255476004</v>
       </c>
       <c r="H125" t="n">
-        <v>3995.928923849488</v>
+        <v>678.5539682008565</v>
       </c>
       <c r="I125" t="n">
-        <v>1.331074137821918</v>
+        <v>0.6217156981184681</v>
       </c>
       <c r="J125" t="n">
-        <v>0.01756163668757283</v>
+        <v>0.004911770261055525</v>
       </c>
       <c r="K125" t="n">
-        <v>0.01678845426446281</v>
+        <v>0.004425714522875817</v>
       </c>
     </row>
     <row r="126">
@@ -5080,34 +5080,34 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>9.297176712894831</v>
+        <v>0.9386287032826731</v>
       </c>
       <c r="C126" t="n">
-        <v>10.62253586548973</v>
+        <v>0.9396858650240912</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1543308637027031</v>
+        <v>0.04578482289846858</v>
       </c>
       <c r="E126" t="n">
-        <v>7.483008659330175</v>
+        <v>1.487586058782504</v>
       </c>
       <c r="F126" t="n">
-        <v>2.80306299585062</v>
+        <v>1.09597237855781</v>
       </c>
       <c r="G126" t="n">
-        <v>4.953146821113633</v>
+        <v>1.050466037229469</v>
       </c>
       <c r="H126" t="n">
-        <v>20272.73960988141</v>
+        <v>3442.540688470428</v>
       </c>
       <c r="I126" t="n">
-        <v>4.758602432110789</v>
+        <v>2.222639407590842</v>
       </c>
       <c r="J126" t="n">
-        <v>0.0740804838398586</v>
+        <v>0.02071938532396045</v>
       </c>
       <c r="K126" t="n">
-        <v>0.01183505923140496</v>
+        <v>0.003119917575163399</v>
       </c>
     </row>
     <row r="127">
@@ -5117,34 +5117,34 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1.180297812244541</v>
+        <v>0.1191610570828355</v>
       </c>
       <c r="C127" t="n">
-        <v>1.60726767672921</v>
+        <v>0.1421813714029686</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3026394465298033</v>
+        <v>0.08978303580384163</v>
       </c>
       <c r="E127" t="n">
-        <v>1.473164770434976</v>
+        <v>0.292858056773218</v>
       </c>
       <c r="F127" t="n">
-        <v>0.7319236910007282</v>
+        <v>0.2861755692741585</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8129569147277559</v>
+        <v>0.1724123389623966</v>
       </c>
       <c r="H127" t="n">
-        <v>3503.85270974663</v>
+        <v>594.9938563720692</v>
       </c>
       <c r="I127" t="n">
-        <v>1.22337285920324</v>
+        <v>0.5714107799159167</v>
       </c>
       <c r="J127" t="n">
-        <v>0.05869388786650378</v>
+        <v>0.01641594676266277</v>
       </c>
       <c r="K127" t="n">
-        <v>0.005190804024793389</v>
+        <v>0.001368381888888889</v>
       </c>
     </row>
     <row r="128">
@@ -5154,34 +5154,34 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4510227229272234</v>
+        <v>0.04553456244249284</v>
       </c>
       <c r="C128" t="n">
-        <v>0.6014633512503884</v>
+        <v>0.05320637337984205</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3558358728233968</v>
+        <v>0.105564642270941</v>
       </c>
       <c r="E128" t="n">
-        <v>1.094451115572876</v>
+        <v>0.2175716073126801</v>
       </c>
       <c r="F128" t="n">
-        <v>0.556099323315003</v>
+        <v>0.2174298255123525</v>
       </c>
       <c r="G128" t="n">
-        <v>1.157546694694308</v>
+        <v>0.2454931245123499</v>
       </c>
       <c r="H128" t="n">
-        <v>10948.61216660938</v>
+        <v>1859.198292443102</v>
       </c>
       <c r="I128" t="n">
-        <v>0.730996596029837</v>
+        <v>0.3414325664583807</v>
       </c>
       <c r="J128" t="n">
-        <v>0.003052476936635802</v>
+        <v>0.0008537396432153258</v>
       </c>
       <c r="K128" t="n">
-        <v>0.002617488946280993</v>
+        <v>0.0006900134259259262</v>
       </c>
     </row>
     <row r="129">
@@ -5191,34 +5191,34 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.729187758629394</v>
+        <v>0.1745761443216896</v>
       </c>
       <c r="C129" t="n">
-        <v>10.08323650963957</v>
+        <v>0.8919786143142699</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2281229014416954</v>
+        <v>0.0676764607610363</v>
       </c>
       <c r="E129" t="n">
-        <v>1.25627118364995</v>
+        <v>0.2497406569906528</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7592584986345544</v>
+        <v>0.2968632327994564</v>
       </c>
       <c r="G129" t="n">
-        <v>1.12420608794914</v>
+        <v>0.2384222307328377</v>
       </c>
       <c r="H129" t="n">
-        <v>3930.010184956443</v>
+        <v>667.3602200869432</v>
       </c>
       <c r="I129" t="n">
-        <v>1.630868905554971</v>
+        <v>0.7617432953929598</v>
       </c>
       <c r="J129" t="n">
-        <v>1.173184357542143e-05</v>
+        <v>3.28125000000068e-06</v>
       </c>
       <c r="K129" t="n">
-        <v>0.01459572032231405</v>
+        <v>0.003847673549019608</v>
       </c>
     </row>
     <row r="130">
@@ -5228,34 +5228,34 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4067507029001582</v>
+        <v>0.04106492719375399</v>
       </c>
       <c r="C130" t="n">
-        <v>0.6459962786841568</v>
+        <v>0.05714582465282925</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1264555669050051</v>
+        <v>0.03751515151515152</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3252525252525253</v>
+        <v>0.06465863453815263</v>
       </c>
       <c r="F130" t="n">
-        <v>0.4377880184331797</v>
+        <v>0.1711711711711712</v>
       </c>
       <c r="G130" t="n">
-        <v>0.6136075949367088</v>
+        <v>0.1301342281879195</v>
       </c>
       <c r="H130" t="n">
-        <v>0.969444444444445</v>
+        <v>0.164622641509434</v>
       </c>
       <c r="I130" t="n">
-        <v>0.6625550660792952</v>
+        <v>0.3094650205761317</v>
       </c>
       <c r="J130" t="n">
-        <v>0.3287709497206704</v>
+        <v>0.091953125</v>
       </c>
       <c r="K130" t="n">
-        <v>0.6889256198347109</v>
+        <v>0.1816122004357299</v>
       </c>
     </row>
     <row r="131">
@@ -5265,34 +5265,34 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.3635575801249272</v>
+        <v>0.0367042157570214</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0632158918030733</v>
+        <v>0.005592175044118022</v>
       </c>
       <c r="D131" t="n">
-        <v>0.1948927477017365</v>
+        <v>0.05781818181818182</v>
       </c>
       <c r="E131" t="n">
-        <v>0.1688888888888889</v>
+        <v>0.03357429718875501</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2172580645161291</v>
+        <v>0.08494594594594594</v>
       </c>
       <c r="G131" t="n">
-        <v>0.3376582278481012</v>
+        <v>0.07161073825503356</v>
       </c>
       <c r="H131" t="n">
-        <v>0.2147222222222226</v>
+        <v>0.03646226415094346</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3211013215859031</v>
+        <v>0.1499794238683128</v>
       </c>
       <c r="J131" t="n">
-        <v>0.1757262569832402</v>
+        <v>0.0491484375</v>
       </c>
       <c r="K131" t="n">
-        <v>0.2131404958677686</v>
+        <v>0.05618736383442265</v>
       </c>
     </row>
     <row r="132">
@@ -5302,34 +5302,34 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.03999405805261105</v>
+        <v>0.004037738768250827</v>
       </c>
       <c r="C132" t="n">
-        <v>0.01025027218778221</v>
+        <v>0.0009067548473807343</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2287027579162411</v>
+        <v>0.06784848484848484</v>
       </c>
       <c r="E132" t="n">
-        <v>0.194141414141414</v>
+        <v>0.03859437751004013</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2093087557603687</v>
+        <v>0.08183783783783784</v>
       </c>
       <c r="G132" t="n">
-        <v>0.3617088607594937</v>
+        <v>0.07671140939597315</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2206111111111106</v>
+        <v>0.03746226415094331</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3244052863436124</v>
+        <v>0.151522633744856</v>
       </c>
       <c r="J132" t="n">
-        <v>0.05418994413407822</v>
+        <v>0.01515625</v>
       </c>
       <c r="K132" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.04793028322440087</v>
       </c>
     </row>
     <row r="133">
@@ -5339,34 +5339,34 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.03937488557784807</v>
+        <v>0.003975228064728432</v>
       </c>
       <c r="C133" t="n">
-        <v>0.006122464243283848</v>
+        <v>0.0005416026061366481</v>
       </c>
       <c r="D133" t="n">
-        <v>0.1185903983656793</v>
+        <v>0.03518181818181818</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0002323232323231843</v>
+        <v>4.618473895581375e-05</v>
       </c>
       <c r="F133" t="n">
-        <v>0.2050230414746544</v>
+        <v>0.08016216216216218</v>
       </c>
       <c r="G133" t="n">
-        <v>0.2005696202531645</v>
+        <v>0.04253691275167786</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1132222222222226</v>
+        <v>0.01922641509433968</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3108810572687226</v>
+        <v>0.1452057613168725</v>
       </c>
       <c r="J133" t="n">
-        <v>0.03583798882681564</v>
+        <v>0.0100234375</v>
       </c>
       <c r="K133" t="n">
-        <v>0.1007438016528926</v>
+        <v>0.02655773420479303</v>
       </c>
     </row>
     <row r="134">
@@ -5376,34 +5376,34 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.3042888823630094</v>
+        <v>0.03072053892227188</v>
       </c>
       <c r="C134" t="n">
-        <v>0.007334519362669552</v>
+        <v>0.0006488228666976911</v>
       </c>
       <c r="D134" t="n">
-        <v>0.1752808988764045</v>
+        <v>0.052</v>
       </c>
       <c r="E134" t="n">
-        <v>0.1329292929292928</v>
+        <v>0.02642570281124496</v>
       </c>
       <c r="F134" t="n">
-        <v>0.2244470046082949</v>
+        <v>0.08775675675675676</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2559493670886075</v>
+        <v>0.05428187919463087</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2598333333333332</v>
+        <v>0.04412264150943394</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2809251101321585</v>
+        <v>0.1312139917695473</v>
       </c>
       <c r="J134" t="n">
-        <v>0.06603351955307263</v>
+        <v>0.01846875</v>
       </c>
       <c r="K134" t="n">
-        <v>0.1274380165289256</v>
+        <v>0.03359477124183007</v>
       </c>
     </row>
     <row r="135">
@@ -5413,34 +5413,34 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.1400424858624462</v>
+        <v>0.01413847461103291</v>
       </c>
       <c r="C135" t="n">
-        <v>0.2136260520824687</v>
+        <v>0.01889768922267993</v>
       </c>
       <c r="D135" t="n">
-        <v>0.3889683350357508</v>
+        <v>0.1153939393939394</v>
       </c>
       <c r="E135" t="n">
-        <v>0.08863636363636364</v>
+        <v>0.01762048192771084</v>
       </c>
       <c r="F135" t="n">
-        <v>0.321889400921659</v>
+        <v>0.1258558558558559</v>
       </c>
       <c r="G135" t="n">
-        <v>1.184177215189874</v>
+        <v>0.2511409395973154</v>
       </c>
       <c r="H135" t="n">
-        <v>1.270555555555555</v>
+        <v>0.215754716981132</v>
       </c>
       <c r="I135" t="n">
-        <v>0.5964757709251101</v>
+        <v>0.2786008230452675</v>
       </c>
       <c r="J135" t="n">
-        <v>2.501675977653632</v>
+        <v>0.6996875000000001</v>
       </c>
       <c r="K135" t="n">
-        <v>0.7643801652892561</v>
+        <v>0.2015032679738562</v>
       </c>
     </row>
     <row r="136">
@@ -5450,34 +5450,34 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.2029954887483544</v>
+        <v>0.02049411324104792</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0820575576692158</v>
+        <v>0.007258937793815244</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3932584269662922</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="E136" t="n">
-        <v>0.459090909090909</v>
+        <v>0.09126506024096383</v>
       </c>
       <c r="F136" t="n">
-        <v>0.6230414746543776</v>
+        <v>0.2436036036036035</v>
       </c>
       <c r="G136" t="n">
-        <v>1.362025316455696</v>
+        <v>0.2888590604026845</v>
       </c>
       <c r="H136" t="n">
-        <v>1.658333333333333</v>
+        <v>0.2816037735849056</v>
       </c>
       <c r="I136" t="n">
-        <v>1.322026431718062</v>
+        <v>0.6174897119341566</v>
       </c>
       <c r="J136" t="n">
-        <v>0.4449720670391062</v>
+        <v>0.124453125</v>
       </c>
       <c r="K136" t="n">
-        <v>0.7473553719008266</v>
+        <v>0.1970152505446623</v>
       </c>
     </row>
     <row r="137">
@@ -5487,34 +5487,34 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2.076817062002376</v>
+        <v>0.209672265684585</v>
       </c>
       <c r="C137" t="n">
-        <v>1.521944839710363</v>
+        <v>0.1346335819743783</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2840653728294179</v>
+        <v>0.0842727272727273</v>
       </c>
       <c r="E137" t="n">
-        <v>2.647474747474747</v>
+        <v>0.526305220883534</v>
       </c>
       <c r="F137" t="n">
-        <v>1.555990783410138</v>
+        <v>0.6083783783783784</v>
       </c>
       <c r="G137" t="n">
-        <v>3.436708860759493</v>
+        <v>0.7288590604026846</v>
       </c>
       <c r="H137" t="n">
-        <v>34.98333333333333</v>
+        <v>5.940566037735849</v>
       </c>
       <c r="I137" t="n">
-        <v>1.38590308370044</v>
+        <v>0.6473251028806583</v>
       </c>
       <c r="J137" t="n">
-        <v>4.614525139664805</v>
+        <v>1.290625</v>
       </c>
       <c r="K137" t="n">
-        <v>1.336363636363636</v>
+        <v>0.3522875816993464</v>
       </c>
     </row>
     <row r="138">
@@ -5524,34 +5524,34 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.1672030577381614</v>
+        <v>0.0168805642956099</v>
       </c>
       <c r="C138" t="n">
-        <v>0.07649802674632222</v>
+        <v>0.006767133135251581</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3875383043922371</v>
+        <v>0.114969696969697</v>
       </c>
       <c r="E138" t="n">
-        <v>0.1447474747474748</v>
+        <v>0.02877510040160643</v>
       </c>
       <c r="F138" t="n">
-        <v>0.3536866359447005</v>
+        <v>0.1382882882882883</v>
       </c>
       <c r="G138" t="n">
-        <v>1.084493670886076</v>
+        <v>0.23</v>
       </c>
       <c r="H138" t="n">
-        <v>0.5536666666666672</v>
+        <v>0.09401886792452838</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7691629955947137</v>
+        <v>0.3592592592592593</v>
       </c>
       <c r="J138" t="n">
-        <v>0.98463687150838</v>
+        <v>0.275390625</v>
       </c>
       <c r="K138" t="n">
-        <v>0.6089256198347109</v>
+        <v>0.1605228758169935</v>
       </c>
     </row>
     <row r="139">
@@ -5561,34 +5561,34 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2.201997725295886</v>
+        <v>0.2223103134803514</v>
       </c>
       <c r="C139" t="n">
-        <v>0.06358950922125546</v>
+        <v>0.005625225815726445</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3579162410623084</v>
+        <v>0.1061818181818182</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4307070707070708</v>
+        <v>0.08562248995983937</v>
       </c>
       <c r="F139" t="n">
-        <v>0.6714285714285715</v>
+        <v>0.2625225225225225</v>
       </c>
       <c r="G139" t="n">
-        <v>1.476898734177215</v>
+        <v>0.313221476510067</v>
       </c>
       <c r="H139" t="n">
-        <v>2.868888888888889</v>
+        <v>0.4871698113207547</v>
       </c>
       <c r="I139" t="n">
-        <v>1.391189427312775</v>
+        <v>0.6497942386831274</v>
       </c>
       <c r="J139" t="n">
-        <v>0.4955307262569832</v>
+        <v>0.13859375</v>
       </c>
       <c r="K139" t="n">
-        <v>0.8884297520661157</v>
+        <v>0.2342047930283224</v>
       </c>
     </row>
     <row r="140">
@@ -5598,34 +5598,34 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.1065866258630696</v>
+        <v>0.01076082229160702</v>
       </c>
       <c r="C140" t="n">
-        <v>3.030859868991375</v>
+        <v>0.2681145268723139</v>
       </c>
       <c r="D140" t="n">
-        <v>0.1798774259448417</v>
+        <v>0.05336363636363636</v>
       </c>
       <c r="E140" t="n">
-        <v>0.8507070707070707</v>
+        <v>0.1691164658634538</v>
       </c>
       <c r="F140" t="n">
-        <v>1.793548387096775</v>
+        <v>0.7012612612612614</v>
       </c>
       <c r="G140" t="n">
-        <v>6.848101265822785</v>
+        <v>1.452348993288591</v>
       </c>
       <c r="H140" t="n">
-        <v>2.355555555555555</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="I140" t="n">
-        <v>1.668281938325991</v>
+        <v>0.7792181069958846</v>
       </c>
       <c r="J140" t="n">
-        <v>4.698324022346369</v>
+        <v>1.3140625</v>
       </c>
       <c r="K140" t="n">
-        <v>2.74380165289256</v>
+        <v>0.7233115468409581</v>
       </c>
     </row>
     <row r="141">
@@ -5635,34 +5635,34 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.1386826639040823</v>
+        <v>0.01400118907146646</v>
       </c>
       <c r="C141" t="n">
-        <v>0.002985667418520558</v>
+        <v>0.0002641167331768186</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4043922369765066</v>
+        <v>0.1199696969696969</v>
       </c>
       <c r="E141" t="n">
-        <v>0.3535353535353536</v>
+        <v>0.07028112449799198</v>
       </c>
       <c r="F141" t="n">
-        <v>0.7880184331797236</v>
+        <v>0.3081081081081081</v>
       </c>
       <c r="G141" t="n">
-        <v>1.206012658227848</v>
+        <v>0.2557718120805369</v>
       </c>
       <c r="H141" t="n">
-        <v>0.3977222222222225</v>
+        <v>0.06753773584905665</v>
       </c>
       <c r="I141" t="n">
-        <v>1.473568281938326</v>
+        <v>0.6882716049382717</v>
       </c>
       <c r="J141" t="n">
-        <v>0.153854748603352</v>
+        <v>0.04303125000000001</v>
       </c>
       <c r="K141" t="n">
-        <v>0.6724793388429752</v>
+        <v>0.177276688453159</v>
       </c>
     </row>
     <row r="142">
@@ -5672,34 +5672,34 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.1573360010094937</v>
+        <v>0.01588440137987221</v>
       </c>
       <c r="C142" t="n">
-        <v>0.05889501067832381</v>
+        <v>0.00520994325231326</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3606741573033708</v>
+        <v>0.107</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4257575757575757</v>
+        <v>0.08463855421686746</v>
       </c>
       <c r="F142" t="n">
-        <v>0.5509216589861752</v>
+        <v>0.2154054054054054</v>
       </c>
       <c r="G142" t="n">
-        <v>1.239556962025316</v>
+        <v>0.2628859060402685</v>
       </c>
       <c r="H142" t="n">
-        <v>2.122777777777777</v>
+        <v>0.3604716981132074</v>
       </c>
       <c r="I142" t="n">
-        <v>1.132158590308371</v>
+        <v>0.5288065843621401</v>
       </c>
       <c r="J142" t="n">
-        <v>0.3966480446927375</v>
+        <v>0.1109375</v>
       </c>
       <c r="K142" t="n">
-        <v>0.7625619834710746</v>
+        <v>0.2010239651416122</v>
       </c>
     </row>
     <row r="143">
@@ -5709,34 +5709,34 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.270945526060443</v>
+        <v>0.02735424480354632</v>
       </c>
       <c r="C143" t="n">
-        <v>0.098973536586366</v>
+        <v>0.0087553513134093</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3043922369765067</v>
+        <v>0.0903030303030303</v>
       </c>
       <c r="E143" t="n">
-        <v>0.1857575757575758</v>
+        <v>0.03692771084337349</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2331797235023041</v>
+        <v>0.09117117117117117</v>
       </c>
       <c r="G143" t="n">
-        <v>0.6012658227848101</v>
+        <v>0.1275167785234899</v>
       </c>
       <c r="H143" t="n">
-        <v>1.031666666666667</v>
+        <v>0.175188679245283</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5691629955947136</v>
+        <v>0.2658436213991769</v>
       </c>
       <c r="J143" t="n">
-        <v>0.255977653631285</v>
+        <v>0.07159375000000001</v>
       </c>
       <c r="K143" t="n">
-        <v>0.3489256198347109</v>
+        <v>0.09198257080610024</v>
       </c>
     </row>
     <row r="144">
@@ -5746,34 +5746,34 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.03726937835092693</v>
+        <v>0.003762659283991345</v>
       </c>
       <c r="C144" t="n">
-        <v>0.03493342831777587</v>
+        <v>0.003090264812726327</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3622063329928498</v>
+        <v>0.1074545454545454</v>
       </c>
       <c r="E144" t="n">
-        <v>0.0005858585858586111</v>
+        <v>0.0001164658634538203</v>
       </c>
       <c r="F144" t="n">
-        <v>0.1857603686635945</v>
+        <v>0.07263063063063062</v>
       </c>
       <c r="G144" t="n">
-        <v>0.354746835443038</v>
+        <v>0.07523489932885907</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1019999999999996</v>
+        <v>0.01732075471698106</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4297356828193834</v>
+        <v>0.2007201646090535</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1311173184357542</v>
+        <v>0.036671875</v>
       </c>
       <c r="K144" t="n">
-        <v>0.2589256198347108</v>
+        <v>0.06825708061002181</v>
       </c>
     </row>
     <row r="145">
@@ -5783,34 +5783,34 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4025152737802848</v>
+        <v>0.04063732476503833</v>
       </c>
       <c r="C145" t="n">
-        <v>0.9771077178431713</v>
+        <v>0.08643645196304976</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E145" t="n">
-        <v>0.09223232323232324</v>
+        <v>0.01833534136546185</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2260829493087558</v>
+        <v>0.0883963963963964</v>
       </c>
       <c r="G145" t="n">
-        <v>0.5598101265822785</v>
+        <v>0.1187248322147651</v>
       </c>
       <c r="H145" t="n">
-        <v>0.3731666666666664</v>
+        <v>0.06336792452830184</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3328634361233481</v>
+        <v>0.1554732510288066</v>
       </c>
       <c r="J145" t="n">
-        <v>0.1946368715083799</v>
+        <v>0.05443750000000001</v>
       </c>
       <c r="K145" t="n">
-        <v>0.2682644628099173</v>
+        <v>0.07071895424836601</v>
       </c>
     </row>
     <row r="146">
@@ -5820,34 +5820,34 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.09236226438151265</v>
+        <v>0.009324752570146325</v>
       </c>
       <c r="C146" t="n">
-        <v>0.5853614465750704</v>
+        <v>0.05178197412010238</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3235955056179777</v>
+        <v>0.09600000000000003</v>
       </c>
       <c r="E146" t="n">
-        <v>2.549494949494949</v>
+        <v>0.5068273092369477</v>
       </c>
       <c r="F146" t="n">
-        <v>1.50852534562212</v>
+        <v>0.5898198198198198</v>
       </c>
       <c r="G146" t="n">
-        <v>1.911075949367089</v>
+        <v>0.4053020134228188</v>
       </c>
       <c r="H146" t="n">
-        <v>2.298888888888889</v>
+        <v>0.3903773584905659</v>
       </c>
       <c r="I146" t="n">
-        <v>1.772687224669604</v>
+        <v>0.8279835390946504</v>
       </c>
       <c r="J146" t="n">
-        <v>1.297486033519553</v>
+        <v>0.3628906249999999</v>
       </c>
       <c r="K146" t="n">
-        <v>1.902479338842975</v>
+        <v>0.5015250544662309</v>
       </c>
     </row>
     <row r="147">
@@ -5857,34 +5857,34 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.2141453945074051</v>
+        <v>0.02161979062758466</v>
       </c>
       <c r="C147" t="n">
-        <v>0.06236562258823614</v>
+        <v>0.005516958921267043</v>
       </c>
       <c r="D147" t="n">
-        <v>0.1240040858018386</v>
+        <v>0.03678787878787879</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3110101010101011</v>
+        <v>0.06182730923694781</v>
       </c>
       <c r="F147" t="n">
-        <v>0.2824884792626728</v>
+        <v>0.1104504504504504</v>
       </c>
       <c r="G147" t="n">
-        <v>0.4025316455696202</v>
+        <v>0.08536912751677853</v>
       </c>
       <c r="H147" t="n">
-        <v>1.136666666666667</v>
+        <v>0.1930188679245284</v>
       </c>
       <c r="I147" t="n">
-        <v>0.375726872246696</v>
+        <v>0.1754938271604938</v>
       </c>
       <c r="J147" t="n">
-        <v>0.1590502793296089</v>
+        <v>0.044484375</v>
       </c>
       <c r="K147" t="n">
-        <v>0.4063636363636364</v>
+        <v>0.107124183006536</v>
       </c>
     </row>
   </sheetData>
